--- a/Data_Election.xlsx
+++ b/Data_Election.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -1020,6 +1020,39 @@
   <si>
     <t>Poid Brique dans la Nuance</t>
   </si>
+  <si>
+    <t>=SI(C2="Gauche Révolutionnaire","Gauche révolutionnaire",</t>
+  </si>
+  <si>
+    <t>SI(OU(C2="PCF",C2="LFI"),"Gauche Radical",</t>
+  </si>
+  <si>
+    <t>SI(C2="EELV","Ecologiste",</t>
+  </si>
+  <si>
+    <t>SI(C2="PS","Gauche Modéré",</t>
+  </si>
+  <si>
+    <t>SI(C2="Centre","Centre",</t>
+  </si>
+  <si>
+    <t>SI(C2="Droite","Droite",</t>
+  </si>
+  <si>
+    <t>SI(OU(C2="Extrême Droite",C2="Extrême Droité"),"Extrême Droite",</t>
+  </si>
+  <si>
+    <t>"")))))))</t>
+  </si>
+  <si>
+    <t>LO/NPA</t>
+  </si>
+  <si>
+    <t>BRIQUE</t>
+  </si>
+  <si>
+    <t>Bloc</t>
+  </si>
 </sst>
 </file>
 
@@ -1032,7 +1065,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1193,6 +1226,11 @@
       <u val="single"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Segoe UI"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="15">
@@ -12934,14 +12972,11 @@
     <col min="3" max="3" width="20.453125" customWidth="1" bestFit="1"/>
     <col min="4" max="4" width="7" customWidth="1" bestFit="1"/>
     <col min="5" max="5" width="23.1796875" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" width="3.54296875" customWidth="1"/>
-    <col min="7" max="7" width="20.08984375" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" width="3.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="20.453125" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" width="18.1796875" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" width="20.453125" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" width="20.453125" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12960,8 +12995,14 @@
       <c r="E1" s="66" t="s">
         <v>264</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" t="s">
         <v>125</v>
+      </c>
+      <c r="H1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I1" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="2">
@@ -12972,17 +13013,22 @@
         <v>23</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D2" s="23"/>
       <c r="E2" s="66">
         <v>1</v>
       </c>
-      <c r="F2"/>
-      <c r="G2" s="82" t="s">
-        <v>128</v>
-      </c>
-      <c r="H2"/>
+      <c r="F2" s="60" t="str">
+        <f>VLOOKUP(C2,$H$2:$I$200,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
+      </c>
+      <c r="H2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I2" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="25">
@@ -13000,11 +13046,16 @@
       <c r="E3" s="68">
         <v>1</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" s="1" t="s">
+      <c r="F3" s="60" t="str">
+        <f>VLOOKUP(C3,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
+      <c r="H3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" t="s">
         <v>126</v>
       </c>
-      <c r="H3"/>
     </row>
     <row r="4">
       <c r="A4" s="25">
@@ -13019,9 +13070,15 @@
       <c r="E4" s="68">
         <v>1</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" s="70" t="s">
-        <v>130</v>
+      <c r="F4" s="60" t="str">
+        <f>VLOOKUP(C4,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
+      <c r="H4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="5">
@@ -13040,8 +13097,14 @@
       <c r="E5" s="68">
         <v>1</v>
       </c>
-      <c r="F5"/>
-      <c r="G5" s="83" t="s">
+      <c r="F5" s="60" t="str">
+        <f>VLOOKUP(C5,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
+      <c r="H5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" t="s">
         <v>133</v>
       </c>
     </row>
@@ -13058,9 +13121,15 @@
       <c r="E6" s="68">
         <v>1</v>
       </c>
-      <c r="F6"/>
-      <c r="G6" s="2" t="s">
-        <v>136</v>
+      <c r="F6" s="60" t="str">
+        <f>VLOOKUP(C6,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
+      <c r="H6" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="7">
@@ -13079,9 +13148,15 @@
       <c r="E7" s="68">
         <v>1</v>
       </c>
-      <c r="F7"/>
-      <c r="G7" s="3" t="s">
-        <v>138</v>
+      <c r="F7" s="60" t="str">
+        <f>VLOOKUP(C7,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
+      <c r="H7" t="s">
+        <v>136</v>
+      </c>
+      <c r="I7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="8">
@@ -13097,9 +13172,15 @@
       <c r="E8" s="68">
         <v>1</v>
       </c>
-      <c r="F8"/>
-      <c r="G8" s="80" t="s">
-        <v>139</v>
+      <c r="F8" s="60" t="str">
+        <f>VLOOKUP(C8,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
+      <c r="H8" t="s">
+        <v>138</v>
+      </c>
+      <c r="I8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -13115,7 +13196,16 @@
       <c r="E9" s="68">
         <v>1</v>
       </c>
-      <c r="F9"/>
+      <c r="F9" s="60" t="str">
+        <f>VLOOKUP(C9,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
+      <c r="H9" t="s">
+        <v>259</v>
+      </c>
+      <c r="I9" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="25">
@@ -13130,7 +13220,10 @@
       <c r="E10" s="68">
         <v>1</v>
       </c>
-      <c r="F10"/>
+      <c r="F10" s="60" t="str">
+        <f>VLOOKUP(C10,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="25">
@@ -13145,7 +13238,10 @@
       <c r="E11" s="68">
         <v>1</v>
       </c>
-      <c r="F11"/>
+      <c r="F11" s="60" t="str">
+        <f>VLOOKUP(C11,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="25">
@@ -13160,8 +13256,10 @@
       <c r="E12" s="68">
         <v>1</v>
       </c>
-      <c r="F12"/>
-      <c r="G12" s="98"/>
+      <c r="F12" s="60" t="str">
+        <f>VLOOKUP(C12,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="25">
@@ -13176,8 +13274,10 @@
       <c r="E13" s="68">
         <v>1</v>
       </c>
-      <c r="F13"/>
-      <c r="G13" s="98"/>
+      <c r="F13" s="60" t="str">
+        <f>VLOOKUP(C13,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="27">
@@ -13193,8 +13293,10 @@
       <c r="E14" s="68">
         <v>1</v>
       </c>
-      <c r="F14"/>
-      <c r="G14" s="98"/>
+      <c r="F14" s="60" t="str">
+        <f>VLOOKUP(C14,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="22">
@@ -13204,14 +13306,16 @@
         <v>23</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D15" s="23"/>
       <c r="E15" s="66">
         <v>1</v>
       </c>
-      <c r="F15"/>
-      <c r="G15" s="98"/>
+      <c r="F15" s="60" t="str">
+        <f>VLOOKUP(C15,$H$2:$I$200,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="25">
@@ -13230,8 +13334,10 @@
         <f>D16/(D16+D17)</f>
         <v>0.4666666666666667</v>
       </c>
-      <c r="F16"/>
-      <c r="G16" s="98"/>
+      <c r="F16" s="60" t="str">
+        <f>VLOOKUP(C16,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="25">
@@ -13250,7 +13356,10 @@
         <f>D17/(D16+D17)</f>
         <v>0.5333333333333333</v>
       </c>
-      <c r="G17" s="98"/>
+      <c r="F17" s="60" t="str">
+        <f>VLOOKUP(C17,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="25">
@@ -13268,8 +13377,10 @@
       <c r="E18" s="68">
         <v>1</v>
       </c>
-      <c r="F18"/>
-      <c r="G18" s="98"/>
+      <c r="F18" s="60" t="str">
+        <f>VLOOKUP(C18,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="25">
@@ -13284,8 +13395,10 @@
       <c r="E19" s="68">
         <v>1</v>
       </c>
-      <c r="F19"/>
-      <c r="G19" s="7"/>
+      <c r="F19" s="60" t="str">
+        <f>VLOOKUP(C19,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="25">
@@ -13300,7 +13413,10 @@
       <c r="E20" s="68">
         <v>1</v>
       </c>
-      <c r="F20"/>
+      <c r="F20" s="60" t="str">
+        <f>VLOOKUP(C20,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="25">
@@ -13318,7 +13434,10 @@
       <c r="E21" s="68">
         <v>1</v>
       </c>
-      <c r="F21"/>
+      <c r="F21" s="60" t="str">
+        <f>VLOOKUP(C21,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="25">
@@ -13333,7 +13452,10 @@
       <c r="E22" s="68">
         <v>1</v>
       </c>
-      <c r="F22"/>
+      <c r="F22" s="60" t="str">
+        <f>VLOOKUP(C22,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="25">
@@ -13348,7 +13470,10 @@
       <c r="E23" s="68">
         <v>1</v>
       </c>
-      <c r="F23"/>
+      <c r="F23" s="60" t="str">
+        <f>VLOOKUP(C23,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="25">
@@ -13363,7 +13488,10 @@
       <c r="E24" s="68">
         <v>1</v>
       </c>
-      <c r="F24"/>
+      <c r="F24" s="60" t="str">
+        <f>VLOOKUP(C24,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="25">
@@ -13378,6 +13506,10 @@
       <c r="E25" s="68">
         <v>1</v>
       </c>
+      <c r="F25" s="60" t="str">
+        <f>VLOOKUP(C25,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="25">
@@ -13392,6 +13524,10 @@
       <c r="E26" s="68">
         <v>1</v>
       </c>
+      <c r="F26" s="60" t="str">
+        <f>VLOOKUP(C26,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="25">
@@ -13406,6 +13542,10 @@
       <c r="E27" s="68">
         <v>1</v>
       </c>
+      <c r="F27" s="60" t="str">
+        <f>VLOOKUP(C27,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="25">
@@ -13420,6 +13560,10 @@
       <c r="E28" s="68">
         <v>1</v>
       </c>
+      <c r="F28" s="60" t="str">
+        <f>VLOOKUP(C28,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="25">
@@ -13434,6 +13578,10 @@
       <c r="E29" s="68">
         <v>1</v>
       </c>
+      <c r="F29" s="60" t="str">
+        <f>VLOOKUP(C29,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="25">
@@ -13448,6 +13596,10 @@
       <c r="E30" s="68">
         <v>1</v>
       </c>
+      <c r="F30" s="60" t="str">
+        <f>VLOOKUP(C30,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="25">
@@ -13462,6 +13614,10 @@
       <c r="E31" s="68">
         <v>1</v>
       </c>
+      <c r="F31" s="60" t="str">
+        <f>VLOOKUP(C31,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="27">
@@ -13477,6 +13633,10 @@
       <c r="E32" s="68">
         <v>1</v>
       </c>
+      <c r="F32" s="60" t="str">
+        <f>VLOOKUP(C32,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="22">
@@ -13486,12 +13646,16 @@
         <v>23</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="66">
         <v>1</v>
       </c>
+      <c r="F33" s="60" t="str">
+        <f>VLOOKUP(C33,$H$2:$I$200,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="25">
@@ -13509,6 +13673,10 @@
       <c r="E34" s="68">
         <v>1</v>
       </c>
+      <c r="F34" s="60" t="str">
+        <f>VLOOKUP(C34,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="25">
@@ -13526,6 +13694,10 @@
       <c r="E35" s="68">
         <v>1</v>
       </c>
+      <c r="F35" s="60" t="str">
+        <f>VLOOKUP(C35,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="25">
@@ -13543,6 +13715,10 @@
       <c r="E36" s="68">
         <v>1</v>
       </c>
+      <c r="F36" s="60" t="str">
+        <f>VLOOKUP(C36,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="25">
@@ -13557,6 +13733,10 @@
       <c r="E37" s="68">
         <v>1</v>
       </c>
+      <c r="F37" s="60" t="str">
+        <f>VLOOKUP(C37,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="25">
@@ -13571,6 +13751,10 @@
       <c r="E38" s="68">
         <v>1</v>
       </c>
+      <c r="F38" s="60" t="str">
+        <f>VLOOKUP(C38,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="25">
@@ -13588,6 +13772,10 @@
       <c r="E39" s="68">
         <v>1</v>
       </c>
+      <c r="F39" s="60" t="str">
+        <f>VLOOKUP(C39,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="25">
@@ -13602,6 +13790,10 @@
       <c r="E40" s="68">
         <v>1</v>
       </c>
+      <c r="F40" s="60" t="str">
+        <f>VLOOKUP(C40,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="25">
@@ -13616,6 +13808,10 @@
       <c r="E41" s="68">
         <v>1</v>
       </c>
+      <c r="F41" s="60" t="str">
+        <f>VLOOKUP(C41,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="25">
@@ -13630,6 +13826,10 @@
       <c r="E42" s="68">
         <v>1</v>
       </c>
+      <c r="F42" s="60" t="str">
+        <f>VLOOKUP(C42,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="25">
@@ -13644,6 +13844,10 @@
       <c r="E43" s="68">
         <v>1</v>
       </c>
+      <c r="F43" s="60" t="str">
+        <f>VLOOKUP(C43,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="25">
@@ -13658,6 +13862,10 @@
       <c r="E44" s="68">
         <v>1</v>
       </c>
+      <c r="F44" s="60" t="str">
+        <f>VLOOKUP(C44,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="25">
@@ -13672,6 +13880,10 @@
       <c r="E45" s="68">
         <v>1</v>
       </c>
+      <c r="F45" s="60" t="str">
+        <f>VLOOKUP(C45,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="25">
@@ -13686,6 +13898,10 @@
       <c r="E46" s="68">
         <v>1</v>
       </c>
+      <c r="F46" s="60" t="str">
+        <f>VLOOKUP(C46,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="25">
@@ -13700,6 +13916,10 @@
       <c r="E47" s="68">
         <v>1</v>
       </c>
+      <c r="F47" s="60" t="str">
+        <f>VLOOKUP(C47,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="25">
@@ -13714,6 +13934,10 @@
       <c r="E48" s="68">
         <v>1</v>
       </c>
+      <c r="F48" s="60" t="str">
+        <f>VLOOKUP(C48,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="27">
@@ -13729,6 +13953,10 @@
       <c r="E49" s="68">
         <v>1</v>
       </c>
+      <c r="F49" s="60" t="str">
+        <f>VLOOKUP(C49,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="22">
@@ -13738,12 +13966,16 @@
         <v>98</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D50" s="23"/>
       <c r="E50" s="66">
         <v>1</v>
       </c>
+      <c r="F50" s="60" t="str">
+        <f>VLOOKUP(C50,$H$2:$I$200,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="25">
@@ -13762,6 +13994,10 @@
         <f>D51/(D51+D52+D53+D54)</f>
         <v>0.14965986394557823</v>
       </c>
+      <c r="F51" s="60" t="str">
+        <f>VLOOKUP(C51,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="25">
@@ -13780,6 +14016,10 @@
         <f>D52/(D51+D52+D53+D54)</f>
         <v>0.5102040816326531</v>
       </c>
+      <c r="F52" s="60" t="str">
+        <f>VLOOKUP(C52,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="25">
@@ -13798,6 +14038,10 @@
         <f>D53/(D51+D52+D53+D54)</f>
         <v>0.1836734693877551</v>
       </c>
+      <c r="F53" s="60" t="str">
+        <f>VLOOKUP(C53,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="25">
@@ -13816,6 +14060,10 @@
         <f>D54/(D51+D52+D53+D54)</f>
         <v>0.1564625850340136</v>
       </c>
+      <c r="F54" s="60" t="str">
+        <f>VLOOKUP(C54,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="25">
@@ -13830,6 +14078,10 @@
       <c r="E55" s="68">
         <v>1</v>
       </c>
+      <c r="F55" s="60" t="str">
+        <f>VLOOKUP(C55,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="25">
@@ -13844,6 +14096,10 @@
       <c r="E56" s="68">
         <v>1</v>
       </c>
+      <c r="F56" s="60" t="str">
+        <f>VLOOKUP(C56,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="25">
@@ -13858,6 +14114,10 @@
       <c r="E57" s="68">
         <v>1</v>
       </c>
+      <c r="F57" s="60" t="str">
+        <f>VLOOKUP(C57,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="25">
@@ -13872,6 +14132,10 @@
       <c r="E58" s="68">
         <v>1</v>
       </c>
+      <c r="F58" s="60" t="str">
+        <f>VLOOKUP(C58,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="25">
@@ -13886,6 +14150,10 @@
       <c r="E59" s="68">
         <v>1</v>
       </c>
+      <c r="F59" s="60" t="str">
+        <f>VLOOKUP(C59,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="25">
@@ -13900,6 +14168,10 @@
       <c r="E60" s="68">
         <v>1</v>
       </c>
+      <c r="F60" s="60" t="str">
+        <f>VLOOKUP(C60,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="25">
@@ -13914,6 +14186,10 @@
       <c r="E61" s="68">
         <v>1</v>
       </c>
+      <c r="F61" s="60" t="str">
+        <f>VLOOKUP(C61,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="25">
@@ -13928,6 +14204,10 @@
       <c r="E62" s="68">
         <v>1</v>
       </c>
+      <c r="F62" s="60" t="str">
+        <f>VLOOKUP(C62,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="25">
@@ -13942,6 +14222,10 @@
       <c r="E63" s="68">
         <v>1</v>
       </c>
+      <c r="F63" s="60" t="str">
+        <f>VLOOKUP(C63,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="25">
@@ -13956,6 +14240,10 @@
       <c r="E64" s="68">
         <v>1</v>
       </c>
+      <c r="F64" s="60" t="str">
+        <f>VLOOKUP(C64,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="25">
@@ -13970,6 +14258,10 @@
       <c r="E65" s="68">
         <v>1</v>
       </c>
+      <c r="F65" s="60" t="str">
+        <f>VLOOKUP(C65,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="25">
@@ -13984,6 +14276,10 @@
       <c r="E66" s="68">
         <v>1</v>
       </c>
+      <c r="F66" s="60" t="str">
+        <f>VLOOKUP(C66,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="25">
@@ -13999,6 +14295,10 @@
       <c r="E67" s="68">
         <v>1</v>
       </c>
+      <c r="F67" s="60" t="str">
+        <f>VLOOKUP(C67,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="27">
@@ -14014,6 +14314,10 @@
       <c r="E68" s="67">
         <v>1</v>
       </c>
+      <c r="F68" s="60" t="str">
+        <f>VLOOKUP(C68,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="22">
@@ -14023,12 +14327,16 @@
         <v>23</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="D69" s="23"/>
       <c r="E69" s="66">
         <v>1</v>
       </c>
+      <c r="F69" s="60" t="str">
+        <f>VLOOKUP(C69,$H$2:$I$200,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="25">
@@ -14043,6 +14351,10 @@
       <c r="E70" s="68">
         <v>1</v>
       </c>
+      <c r="F70" s="60" t="str">
+        <f>VLOOKUP(C70,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="25">
@@ -14057,6 +14369,10 @@
       <c r="E71" s="68">
         <v>1</v>
       </c>
+      <c r="F71" s="60" t="str">
+        <f>VLOOKUP(C71,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="25">
@@ -14075,6 +14391,10 @@
         <f>D72/(D72+D73+D74+D75)</f>
         <v>8.808290155440414E-2</v>
       </c>
+      <c r="F72" s="60" t="str">
+        <f>VLOOKUP(C72,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="25">
@@ -14093,6 +14413,10 @@
         <f>D73/(D72+D73+D74+D75)</f>
         <v>0.37305699481865284</v>
       </c>
+      <c r="F73" s="60" t="str">
+        <f>VLOOKUP(C73,$H$2:$I$200,2,0)</f>
+        <v>Gauche Radical</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="25">
@@ -14111,6 +14435,10 @@
         <f>D74/(D72+D73+D74+D75)</f>
         <v>0.34196891191709844</v>
       </c>
+      <c r="F74" s="60" t="str">
+        <f>VLOOKUP(C74,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="25">
@@ -14129,6 +14457,10 @@
         <f>D75/(D72+D73+D74+D75)</f>
         <v>0.19689119170984457</v>
       </c>
+      <c r="F75" s="60" t="str">
+        <f>VLOOKUP(C75,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="25">
@@ -14143,6 +14475,10 @@
       <c r="E76" s="68">
         <v>1</v>
       </c>
+      <c r="F76" s="60" t="str">
+        <f>VLOOKUP(C76,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="25">
@@ -14157,6 +14493,10 @@
       <c r="E77" s="68">
         <v>1</v>
       </c>
+      <c r="F77" s="60" t="str">
+        <f>VLOOKUP(C77,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="25">
@@ -14171,6 +14511,10 @@
       <c r="E78" s="68">
         <v>1</v>
       </c>
+      <c r="F78" s="60" t="str">
+        <f>VLOOKUP(C78,$H$2:$I$200,2,0)</f>
+        <v>Gauche Modéré</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="25">
@@ -14185,6 +14529,10 @@
       <c r="E79" s="68">
         <v>1</v>
       </c>
+      <c r="F79" s="60" t="str">
+        <f>VLOOKUP(C79,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="25">
@@ -14199,6 +14547,10 @@
       <c r="E80" s="68">
         <v>1</v>
       </c>
+      <c r="F80" s="60" t="str">
+        <f>VLOOKUP(C80,$H$2:$I$200,2,0)</f>
+        <v>Ecologiste</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="25">
@@ -14213,6 +14565,10 @@
       <c r="E81" s="68">
         <v>1</v>
       </c>
+      <c r="F81" s="60" t="str">
+        <f>VLOOKUP(C81,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="25">
@@ -14227,6 +14583,10 @@
       <c r="E82" s="68">
         <v>1</v>
       </c>
+      <c r="F82" s="60" t="str">
+        <f>VLOOKUP(C82,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="25">
@@ -14241,6 +14601,10 @@
       <c r="E83" s="68">
         <v>1</v>
       </c>
+      <c r="F83" s="60" t="str">
+        <f>VLOOKUP(C83,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="25">
@@ -14255,6 +14619,10 @@
       <c r="E84" s="68">
         <v>1</v>
       </c>
+      <c r="F84" s="60" t="str">
+        <f>VLOOKUP(C84,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="25">
@@ -14269,6 +14637,10 @@
       <c r="E85" s="68">
         <v>1</v>
       </c>
+      <c r="F85" s="60" t="str">
+        <f>VLOOKUP(C85,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="25">
@@ -14283,6 +14655,10 @@
       <c r="E86" s="68">
         <v>1</v>
       </c>
+      <c r="F86" s="60" t="str">
+        <f>VLOOKUP(C86,$H$2:$I$200,2,0)</f>
+        <v>Centre</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="25">
@@ -14297,6 +14673,10 @@
       <c r="E87" s="68">
         <v>1</v>
       </c>
+      <c r="F87" s="60" t="str">
+        <f>VLOOKUP(C87,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="25">
@@ -14311,6 +14691,10 @@
       <c r="E88" s="68">
         <v>1</v>
       </c>
+      <c r="F88" s="60" t="str">
+        <f>VLOOKUP(C88,$H$2:$I$200,2,0)</f>
+        <v>Droite</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="25">
@@ -14325,6 +14709,10 @@
       <c r="E89" s="68">
         <v>1</v>
       </c>
+      <c r="F89" s="60" t="str">
+        <f>VLOOKUP(C89,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="25">
@@ -14339,6 +14727,10 @@
       <c r="E90" s="68">
         <v>1</v>
       </c>
+      <c r="F90" s="60" t="str">
+        <f>VLOOKUP(C90,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="25">
@@ -14353,6 +14745,10 @@
       <c r="E91" s="68">
         <v>1</v>
       </c>
+      <c r="F91" s="60" t="str">
+        <f>VLOOKUP(C91,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="25">
@@ -14367,6 +14763,10 @@
       <c r="E92" s="68">
         <v>1</v>
       </c>
+      <c r="F92" s="60" t="str">
+        <f>VLOOKUP(C92,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="27">
@@ -14381,6 +14781,10 @@
       <c r="D93" s="28"/>
       <c r="E93" s="67">
         <v>1</v>
+      </c>
+      <c r="F93" s="60" t="str">
+        <f>VLOOKUP(C93,$H$2:$I$200,2,0)</f>
+        <v>Extrème Droite</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Election.xlsx
+++ b/Data_Election.xlsx
@@ -1306,7 +1306,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1578,11 +1578,22 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" xfId="0"/>
@@ -1703,6 +1714,7 @@
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="26" applyBorder="1" applyAlignment="1" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5117,7 +5129,7 @@
         <v>36054394</v>
       </c>
       <c r="J86" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K86">
         <v>7059951</v>
@@ -5585,7 +5597,7 @@
         <v>139577</v>
       </c>
       <c r="J99" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K99">
         <v>25419</v>
@@ -8291,7 +8303,7 @@
         <v>35132947</v>
       </c>
       <c r="J174" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K174">
         <v>1627853</v>
@@ -8365,7 +8377,7 @@
         <v>35132947</v>
       </c>
       <c r="J176" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="K176">
         <v>802422</v>
@@ -8439,7 +8451,7 @@
         <v>35132947</v>
       </c>
       <c r="J178" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="K178">
         <v>616478</v>
@@ -8846,7 +8858,7 @@
         <v>139655</v>
       </c>
       <c r="J189" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K189">
         <v>5796</v>
@@ -8883,7 +8895,7 @@
         <v>139655</v>
       </c>
       <c r="J190" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="K190">
         <v>3493</v>
@@ -8957,7 +8969,7 @@
         <v>139655</v>
       </c>
       <c r="J192" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="K192">
         <v>2491</v>
@@ -9290,7 +9302,7 @@
         <v>22744708</v>
       </c>
       <c r="J201" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K201">
         <v>608314</v>
@@ -10363,7 +10375,7 @@
         <v>52395</v>
       </c>
       <c r="J230" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K230">
         <v>1283</v>
@@ -10400,7 +10412,7 @@
         <v>52395</v>
       </c>
       <c r="J231" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K231">
         <v>663</v>
@@ -10733,7 +10745,7 @@
         <v>41266</v>
       </c>
       <c r="J240" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K240">
         <v>856</v>
@@ -10770,7 +10782,7 @@
         <v>41266</v>
       </c>
       <c r="J241" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="K241">
         <v>578</v>
@@ -13020,7 +13032,7 @@
         <v>1</v>
       </c>
       <c r="F2" s="60" t="str">
-        <f>VLOOKUP(C2,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C2,$H$2:$I$203,2,0)</f>
         <v>Gauche Révolutionnaire</v>
       </c>
       <c r="H2" t="s">
@@ -13047,7 +13059,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="60" t="str">
-        <f>VLOOKUP(C3,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C3,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
       </c>
       <c r="H3" t="s">
@@ -13071,7 +13083,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="60" t="str">
-        <f>VLOOKUP(C4,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C4,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
       <c r="H4" t="s">
@@ -13098,7 +13110,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="60" t="str">
-        <f>VLOOKUP(C5,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C5,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
       <c r="H5" t="s">
@@ -13122,7 +13134,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="60" t="str">
-        <f>VLOOKUP(C6,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C6,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
       <c r="H6" t="s">
@@ -13149,7 +13161,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="60" t="str">
-        <f>VLOOKUP(C7,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C7,$H$2:$I$203,2,0)</f>
         <v>Ecologiste</v>
       </c>
       <c r="H7" t="s">
@@ -13173,7 +13185,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="60" t="str">
-        <f>VLOOKUP(C8,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C8,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
       <c r="H8" t="s">
@@ -13197,7 +13209,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="60" t="str">
-        <f>VLOOKUP(C9,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C9,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
       <c r="H9" t="s">
@@ -13221,7 +13233,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="60" t="str">
-        <f>VLOOKUP(C10,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C10,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13239,7 +13251,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="60" t="str">
-        <f>VLOOKUP(C11,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C11,$H$2:$I$203,2,0)</f>
         <v>Droite</v>
       </c>
     </row>
@@ -13257,7 +13269,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="60" t="str">
-        <f>VLOOKUP(C12,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C12,$H$2:$I$203,2,0)</f>
         <v>Droite</v>
       </c>
     </row>
@@ -13275,7 +13287,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="60" t="str">
-        <f>VLOOKUP(C13,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C13,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>
@@ -13294,7 +13306,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="60" t="str">
-        <f>VLOOKUP(C14,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C14,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>
@@ -13313,7 +13325,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="60" t="str">
-        <f>VLOOKUP(C15,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C15,$H$2:$I$203,2,0)</f>
         <v>Gauche Révolutionnaire</v>
       </c>
     </row>
@@ -13335,7 +13347,7 @@
         <v>0.4666666666666667</v>
       </c>
       <c r="F16" s="60" t="str">
-        <f>VLOOKUP(C16,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C16,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
       </c>
     </row>
@@ -13357,7 +13369,7 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="F17" s="60" t="str">
-        <f>VLOOKUP(C17,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C17,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
       </c>
     </row>
@@ -13378,7 +13390,7 @@
         <v>1</v>
       </c>
       <c r="F18" s="60" t="str">
-        <f>VLOOKUP(C18,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C18,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
     </row>
@@ -13396,7 +13408,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="60" t="str">
-        <f>VLOOKUP(C19,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C19,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
     </row>
@@ -13414,7 +13426,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="60" t="str">
-        <f>VLOOKUP(C20,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C20,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
     </row>
@@ -13435,7 +13447,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="60" t="str">
-        <f>VLOOKUP(C21,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C21,$H$2:$I$203,2,0)</f>
         <v>Ecologiste</v>
       </c>
     </row>
@@ -13443,18 +13455,18 @@
       <c r="A22" s="25">
         <v>2012</v>
       </c>
-      <c r="B22" s="93" t="s">
-        <v>45</v>
+      <c r="B22" s="92" t="s">
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E22" s="68">
         <v>1</v>
       </c>
       <c r="F22" s="60" t="str">
-        <f>VLOOKUP(C22,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C22,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="23">
@@ -13462,7 +13474,7 @@
         <v>2012</v>
       </c>
       <c r="B23" s="93" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
         <v>136</v>
@@ -13471,7 +13483,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="60" t="str">
-        <f>VLOOKUP(C23,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C23,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13480,7 +13492,7 @@
         <v>2012</v>
       </c>
       <c r="B24" s="93" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
         <v>136</v>
@@ -13489,7 +13501,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="60" t="str">
-        <f>VLOOKUP(C24,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C24,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13498,7 +13510,7 @@
         <v>2012</v>
       </c>
       <c r="B25" s="93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>136</v>
@@ -13507,7 +13519,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="60" t="str">
-        <f>VLOOKUP(C25,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C25,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13516,7 +13528,7 @@
         <v>2012</v>
       </c>
       <c r="B26" s="93" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
         <v>136</v>
@@ -13525,7 +13537,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="60" t="str">
-        <f>VLOOKUP(C26,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C26,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13534,7 +13546,7 @@
         <v>2012</v>
       </c>
       <c r="B27" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
         <v>136</v>
@@ -13543,7 +13555,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="60" t="str">
-        <f>VLOOKUP(C27,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C27,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13552,7 +13564,7 @@
         <v>2012</v>
       </c>
       <c r="B28" s="93" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
         <v>136</v>
@@ -13561,7 +13573,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="60" t="str">
-        <f>VLOOKUP(C28,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C28,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13569,18 +13581,18 @@
       <c r="A29" s="25">
         <v>2012</v>
       </c>
-      <c r="B29" s="94" t="s">
-        <v>21</v>
+      <c r="B29" s="93" t="s">
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E29" s="68">
         <v>1</v>
       </c>
       <c r="F29" s="60" t="str">
-        <f>VLOOKUP(C29,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C29,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="30">
@@ -13588,7 +13600,7 @@
         <v>2012</v>
       </c>
       <c r="B30" s="94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C30" t="s">
         <v>138</v>
@@ -13597,7 +13609,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="60" t="str">
-        <f>VLOOKUP(C30,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C30,$H$2:$I$203,2,0)</f>
         <v>Droite</v>
       </c>
     </row>
@@ -13605,230 +13617,234 @@
       <c r="A31" s="25">
         <v>2012</v>
       </c>
-      <c r="B31" s="95" t="s">
-        <v>20</v>
+      <c r="B31" s="94" t="s">
+        <v>26</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="E31" s="68">
         <v>1</v>
       </c>
       <c r="F31" s="60" t="str">
-        <f>VLOOKUP(C31,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C31,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="27">
+      <c r="A32" s="25">
         <v>2012</v>
       </c>
-      <c r="B32" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="28" t="s">
+      <c r="B32" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C32" t="s">
         <v>259</v>
       </c>
-      <c r="D32" s="28"/>
       <c r="E32" s="68">
         <v>1</v>
       </c>
       <c r="F32" s="60" t="str">
-        <f>VLOOKUP(C32,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C32,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="22">
+      <c r="A33" s="27">
+        <v>2012</v>
+      </c>
+      <c r="B33" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="68">
+        <v>1</v>
+      </c>
+      <c r="F33" s="60" t="str">
+        <f>VLOOKUP(C33,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
         <v>2017</v>
       </c>
-      <c r="B33" s="109" t="s">
+      <c r="B34" s="82" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C34" t="s">
         <v>273</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="66">
+      <c r="D34"/>
+      <c r="E34">
         <v>1</v>
       </c>
-      <c r="F33" s="60" t="str">
-        <f>VLOOKUP(C33,$H$2:$I$200,2,0)</f>
+      <c r="F34" s="60" t="str">
+        <f>VLOOKUP(C34,$H$2:$I$203,2,0)</f>
         <v>Gauche Révolutionnaire</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="25">
+    <row r="35">
+      <c r="A35">
         <v>2017</v>
       </c>
-      <c r="B34" s="90" t="s">
+      <c r="B35" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>157</v>
       </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34" s="68">
+      <c r="D35"/>
+      <c r="E35">
         <v>1</v>
       </c>
-      <c r="F34" s="60" t="str">
-        <f>VLOOKUP(C34,$H$2:$I$200,2,0)</f>
+      <c r="F35" s="60" t="str">
+        <f>VLOOKUP(C35,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="25">
+    <row r="36">
+      <c r="A36">
         <v>2017</v>
       </c>
-      <c r="B35" s="90" t="s">
+      <c r="B36" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>38</v>
       </c>
-      <c r="D35">
-        <v>17</v>
-      </c>
-      <c r="E35" s="68">
+      <c r="D36"/>
+      <c r="E36">
         <v>1</v>
       </c>
-      <c r="F35" s="60" t="str">
-        <f>VLOOKUP(C35,$H$2:$I$200,2,0)</f>
+      <c r="F36" s="60" t="str">
+        <f>VLOOKUP(C36,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B36" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36">
-        <v>28</v>
-      </c>
-      <c r="E36" s="68">
-        <v>1</v>
-      </c>
-      <c r="F36" s="60" t="str">
-        <f>VLOOKUP(C36,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25">
         <v>2017</v>
       </c>
-      <c r="B37" s="91" t="s">
-        <v>50</v>
+      <c r="B37" s="90" t="s">
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>157</v>
+      </c>
+      <c r="D37">
+        <v>16</v>
       </c>
       <c r="E37" s="68">
-        <v>1</v>
+        <f>D37/(D37+D38)</f>
+        <v>0.48484848484848486</v>
       </c>
       <c r="F37" s="60" t="str">
-        <f>VLOOKUP(C37,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C37,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25">
         <v>2017</v>
       </c>
-      <c r="B38" s="91" t="s">
-        <v>43</v>
+      <c r="B38" s="90" t="s">
+        <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>38</v>
+      </c>
+      <c r="D38">
+        <v>17</v>
       </c>
       <c r="E38" s="68">
-        <v>1</v>
+        <f>D38/(D37+D38)</f>
+        <v>0.5151515151515151</v>
       </c>
       <c r="F38" s="60" t="str">
-        <f>VLOOKUP(C38,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C38,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25">
         <v>2017</v>
       </c>
-      <c r="B39" s="97" t="s">
-        <v>14</v>
+      <c r="B39" s="91" t="s">
+        <v>33</v>
       </c>
       <c r="C39" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E39" s="68">
         <v>1</v>
       </c>
       <c r="F39" s="60" t="str">
-        <f>VLOOKUP(C39,$H$2:$I$200,2,0)</f>
-        <v>Ecologiste</v>
+        <f>VLOOKUP(C39,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25">
         <v>2017</v>
       </c>
-      <c r="B40" s="93" t="s">
-        <v>35</v>
+      <c r="B40" s="91" t="s">
+        <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E40" s="68">
         <v>1</v>
       </c>
       <c r="F40" s="60" t="str">
-        <f>VLOOKUP(C40,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C40,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25">
         <v>2017</v>
       </c>
-      <c r="B41" s="93" t="s">
-        <v>45</v>
+      <c r="B41" s="91" t="s">
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E41" s="68">
         <v>1</v>
       </c>
       <c r="F41" s="60" t="str">
-        <f>VLOOKUP(C41,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C41,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25">
         <v>2017</v>
       </c>
-      <c r="B42" s="93" t="s">
-        <v>30</v>
+      <c r="B42" s="97" t="s">
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>131</v>
+      </c>
+      <c r="D42">
+        <v>3</v>
       </c>
       <c r="E42" s="68">
         <v>1</v>
       </c>
       <c r="F42" s="60" t="str">
-        <f>VLOOKUP(C42,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C42,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="43">
@@ -13836,7 +13852,7 @@
         <v>2017</v>
       </c>
       <c r="B43" s="93" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
         <v>136</v>
@@ -13845,7 +13861,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="60" t="str">
-        <f>VLOOKUP(C43,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C43,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13854,7 +13870,7 @@
         <v>2017</v>
       </c>
       <c r="B44" s="93" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C44" t="s">
         <v>136</v>
@@ -13863,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="60" t="str">
-        <f>VLOOKUP(C44,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C44,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -13871,176 +13887,164 @@
       <c r="A45" s="25">
         <v>2017</v>
       </c>
-      <c r="B45" s="94" t="s">
-        <v>31</v>
+      <c r="B45" s="93" t="s">
+        <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E45" s="68">
         <v>1</v>
       </c>
       <c r="F45" s="60" t="str">
-        <f>VLOOKUP(C45,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C45,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25">
         <v>2017</v>
       </c>
-      <c r="B46" s="94" t="s">
-        <v>26</v>
+      <c r="B46" s="93" t="s">
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E46" s="68">
         <v>1</v>
       </c>
       <c r="F46" s="60" t="str">
-        <f>VLOOKUP(C46,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C46,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25">
         <v>2017</v>
       </c>
-      <c r="B47" s="95" t="s">
-        <v>34</v>
+      <c r="B47" s="93" t="s">
+        <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="E47" s="68">
         <v>1</v>
       </c>
       <c r="F47" s="60" t="str">
-        <f>VLOOKUP(C47,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C47,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25">
         <v>2017</v>
       </c>
-      <c r="B48" s="95" t="s">
-        <v>20</v>
+      <c r="B48" s="94" t="s">
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="E48" s="68">
         <v>1</v>
       </c>
       <c r="F48" s="60" t="str">
-        <f>VLOOKUP(C48,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C48,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="27">
+      <c r="A49" s="25">
         <v>2017</v>
       </c>
-      <c r="B49" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D49" s="28"/>
+      <c r="B49" s="94" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>138</v>
+      </c>
       <c r="E49" s="68">
         <v>1</v>
       </c>
       <c r="F49" s="60" t="str">
-        <f>VLOOKUP(C49,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C49,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25">
+        <v>2017</v>
+      </c>
+      <c r="B50" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" t="s">
+        <v>259</v>
+      </c>
+      <c r="E50" s="68">
+        <v>1</v>
+      </c>
+      <c r="F50" s="60" t="str">
+        <f>VLOOKUP(C50,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="22">
-        <v>2022</v>
-      </c>
-      <c r="B50" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="66">
-        <v>1</v>
-      </c>
-      <c r="F50" s="60" t="str">
-        <f>VLOOKUP(C50,$H$2:$I$200,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25">
+        <v>2017</v>
+      </c>
+      <c r="B51" s="95" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
+        <v>259</v>
+      </c>
+      <c r="E51" s="68">
+        <v>1</v>
+      </c>
+      <c r="F51" s="60" t="str">
+        <f>VLOOKUP(C51,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="27">
+        <v>2017</v>
+      </c>
+      <c r="B52" s="96" t="s">
+        <v>49</v>
+      </c>
+      <c r="C52" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="D52" s="28"/>
+      <c r="E52" s="68">
+        <v>1</v>
+      </c>
+      <c r="F52" s="60" t="str">
+        <f>VLOOKUP(C52,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22">
         <v>2022</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C51" t="s">
-        <v>157</v>
-      </c>
-      <c r="D51">
-        <v>22</v>
-      </c>
-      <c r="E51" s="68">
-        <f>D51/(D51+D52+D53+D54)</f>
-        <v>0.14965986394557823</v>
-      </c>
-      <c r="F51" s="60" t="str">
-        <f>VLOOKUP(C51,$H$2:$I$200,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52">
-        <v>75</v>
-      </c>
-      <c r="E52" s="68">
-        <f>D52/(D51+D52+D53+D54)</f>
-        <v>0.5102040816326531</v>
-      </c>
-      <c r="F52" s="60" t="str">
-        <f>VLOOKUP(C52,$H$2:$I$200,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D53">
-        <v>27</v>
-      </c>
-      <c r="E53" s="68">
-        <f>D53/(D51+D52+D53+D54)</f>
-        <v>0.1836734693877551</v>
+      <c r="B53" s="84" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D53" s="23"/>
+      <c r="E53" s="66">
+        <v>1</v>
       </c>
       <c r="F53" s="60" t="str">
-        <f>VLOOKUP(C53,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C53,$H$2:$I$203,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
       </c>
     </row>
     <row r="54">
@@ -14051,53 +14055,61 @@
         <v>99</v>
       </c>
       <c r="C54" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="D54">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E54" s="68">
-        <f>D54/(D51+D52+D53+D54)</f>
-        <v>0.1564625850340136</v>
+        <f>D54/(D54+D55+D56+D57)</f>
+        <v>0.14965986394557823</v>
       </c>
       <c r="F54" s="60" t="str">
-        <f>VLOOKUP(C54,$H$2:$I$200,2,0)</f>
-        <v>Ecologiste</v>
+        <f>VLOOKUP(C54,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25">
         <v>2022</v>
       </c>
-      <c r="B55" s="75" t="s">
-        <v>50</v>
+      <c r="B55" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>38</v>
+      </c>
+      <c r="D55">
+        <v>75</v>
       </c>
       <c r="E55" s="68">
-        <v>1</v>
+        <f>D55/(D54+D55+D56+D57)</f>
+        <v>0.5102040816326531</v>
       </c>
       <c r="F55" s="60" t="str">
-        <f>VLOOKUP(C55,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C55,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25">
         <v>2022</v>
       </c>
-      <c r="B56" s="75" t="s">
-        <v>43</v>
+      <c r="B56" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C56" t="s">
         <v>134</v>
       </c>
+      <c r="D56">
+        <v>27</v>
+      </c>
       <c r="E56" s="68">
-        <v>1</v>
+        <f>D56/(D54+D55+D56+D57)</f>
+        <v>0.1836734693877551</v>
       </c>
       <c r="F56" s="60" t="str">
-        <f>VLOOKUP(C56,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C56,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
     </row>
@@ -14105,17 +14117,21 @@
       <c r="A57" s="25">
         <v>2022</v>
       </c>
-      <c r="B57" s="88" t="s">
-        <v>14</v>
+      <c r="B57" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="C57" t="s">
         <v>131</v>
       </c>
+      <c r="D57">
+        <v>23</v>
+      </c>
       <c r="E57" s="68">
-        <v>1</v>
+        <f>D57/(D54+D55+D56+D57)</f>
+        <v>0.1564625850340136</v>
       </c>
       <c r="F57" s="60" t="str">
-        <f>VLOOKUP(C57,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C57,$H$2:$I$203,2,0)</f>
         <v>Ecologiste</v>
       </c>
     </row>
@@ -14123,54 +14139,54 @@
       <c r="A58" s="25">
         <v>2022</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>35</v>
+      <c r="B58" s="75" t="s">
+        <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E58" s="68">
         <v>1</v>
       </c>
       <c r="F58" s="60" t="str">
-        <f>VLOOKUP(C58,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C58,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25">
         <v>2022</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>45</v>
+      <c r="B59" s="75" t="s">
+        <v>43</v>
       </c>
       <c r="C59" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59" s="68">
         <v>1</v>
       </c>
       <c r="F59" s="60" t="str">
-        <f>VLOOKUP(C59,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C59,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25">
         <v>2022</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>36</v>
+      <c r="B60" s="88" t="s">
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E60" s="68">
         <v>1</v>
       </c>
       <c r="F60" s="60" t="str">
-        <f>VLOOKUP(C60,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C60,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="61">
@@ -14178,7 +14194,7 @@
         <v>2022</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C61" t="s">
         <v>136</v>
@@ -14187,7 +14203,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="60" t="str">
-        <f>VLOOKUP(C61,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C61,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -14196,7 +14212,7 @@
         <v>2022</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
         <v>136</v>
@@ -14205,7 +14221,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="60" t="str">
-        <f>VLOOKUP(C62,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C62,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -14213,187 +14229,183 @@
       <c r="A63" s="25">
         <v>2022</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
+      <c r="B63" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C63" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E63" s="68">
         <v>1</v>
       </c>
       <c r="F63" s="60" t="str">
-        <f>VLOOKUP(C63,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C63,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25">
         <v>2022</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>26</v>
+      <c r="B64" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C64" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E64" s="68">
         <v>1</v>
       </c>
       <c r="F64" s="60" t="str">
-        <f>VLOOKUP(C64,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C64,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25">
         <v>2022</v>
       </c>
-      <c r="B65" s="80" t="s">
-        <v>48</v>
+      <c r="B65" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="E65" s="68">
         <v>1</v>
       </c>
       <c r="F65" s="60" t="str">
-        <f>VLOOKUP(C65,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C65,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="25">
         <v>2022</v>
       </c>
-      <c r="B66" s="80" t="s">
-        <v>39</v>
+      <c r="B66" s="3" t="s">
+        <v>31</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="E66" s="68">
         <v>1</v>
       </c>
       <c r="F66" s="60" t="str">
-        <f>VLOOKUP(C66,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C66,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="25">
         <v>2022</v>
       </c>
-      <c r="B67" s="80" t="s">
-        <v>37</v>
+      <c r="B67" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>259</v>
-      </c>
-      <c r="D67"/>
+        <v>138</v>
+      </c>
       <c r="E67" s="68">
         <v>1</v>
       </c>
       <c r="F67" s="60" t="str">
-        <f>VLOOKUP(C67,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C67,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="25">
+        <v>2022</v>
+      </c>
+      <c r="B68" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" t="s">
+        <v>259</v>
+      </c>
+      <c r="E68" s="68">
+        <v>1</v>
+      </c>
+      <c r="F68" s="60" t="str">
+        <f>VLOOKUP(C68,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="27">
+    <row r="69">
+      <c r="A69" s="25">
         <v>2022</v>
       </c>
-      <c r="B68" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="C68" s="28" t="s">
+      <c r="B69" s="80" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" t="s">
         <v>259</v>
       </c>
-      <c r="D68" s="28"/>
-      <c r="E68" s="67">
+      <c r="E69" s="68">
         <v>1</v>
       </c>
-      <c r="F68" s="60" t="str">
-        <f>VLOOKUP(C68,$H$2:$I$200,2,0)</f>
+      <c r="F69" s="60" t="str">
+        <f>VLOOKUP(C69,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="22">
-        <v>2024</v>
-      </c>
-      <c r="B69" s="109" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D69" s="23"/>
-      <c r="E69" s="66">
-        <v>1</v>
-      </c>
-      <c r="F69" s="60" t="str">
-        <f>VLOOKUP(C69,$H$2:$I$200,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B70" s="90" t="s">
-        <v>40</v>
+        <v>2022</v>
+      </c>
+      <c r="B70" s="80" t="s">
+        <v>37</v>
       </c>
       <c r="C70" t="s">
-        <v>157</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D70"/>
       <c r="E70" s="68">
         <v>1</v>
       </c>
       <c r="F70" s="60" t="str">
-        <f>VLOOKUP(C70,$H$2:$I$200,2,0)</f>
-        <v>Gauche Radical</v>
+        <f>VLOOKUP(C70,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="25">
+      <c r="A71" s="27">
+        <v>2022</v>
+      </c>
+      <c r="B71" s="81" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="28" t="s">
+        <v>259</v>
+      </c>
+      <c r="D71" s="28"/>
+      <c r="E71" s="67">
+        <v>1</v>
+      </c>
+      <c r="F71" s="60" t="str">
+        <f>VLOOKUP(C71,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22">
         <v>2024</v>
       </c>
-      <c r="B71" s="90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C71" t="s">
-        <v>38</v>
-      </c>
-      <c r="E71" s="68">
+      <c r="B72" s="109" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D72" s="23"/>
+      <c r="E72" s="66">
         <v>1</v>
       </c>
-      <c r="F71" s="60" t="str">
-        <f>VLOOKUP(C71,$H$2:$I$200,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B72" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C72" t="s">
-        <v>157</v>
-      </c>
-      <c r="D72">
-        <v>17</v>
-      </c>
-      <c r="E72" s="68">
-        <f>D72/(D72+D73+D74+D75)</f>
-        <v>8.808290155440414E-2</v>
-      </c>
       <c r="F72" s="60" t="str">
-        <f>VLOOKUP(C72,$H$2:$I$200,2,0)</f>
-        <v>Gauche Radical</v>
+        <f>VLOOKUP(C72,$H$2:$I$203,2,0)</f>
+        <v>Gauche Révolutionnaire</v>
       </c>
     </row>
     <row r="73">
@@ -14401,20 +14413,16 @@
         <v>2024</v>
       </c>
       <c r="B73" s="90" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C73" t="s">
-        <v>38</v>
-      </c>
-      <c r="D73">
-        <v>72</v>
+        <v>157</v>
       </c>
       <c r="E73" s="68">
-        <f>D73/(D72+D73+D74+D75)</f>
-        <v>0.37305699481865284</v>
+        <v>1</v>
       </c>
       <c r="F73" s="60" t="str">
-        <f>VLOOKUP(C73,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C73,$H$2:$I$203,2,0)</f>
         <v>Gauche Radical</v>
       </c>
     </row>
@@ -14423,21 +14431,17 @@
         <v>2024</v>
       </c>
       <c r="B74" s="90" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
-      </c>
-      <c r="D74">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E74" s="68">
-        <f>D74/(D72+D73+D74+D75)</f>
-        <v>0.34196891191709844</v>
+        <v>1</v>
       </c>
       <c r="F74" s="60" t="str">
-        <f>VLOOKUP(C74,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C74,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="75">
@@ -14448,53 +14452,61 @@
         <v>41</v>
       </c>
       <c r="C75" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="D75">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="E75" s="68">
-        <f>D75/(D72+D73+D74+D75)</f>
-        <v>0.19689119170984457</v>
+        <f>D75/(D75+D76+D77+D78)</f>
+        <v>8.808290155440414E-2</v>
       </c>
       <c r="F75" s="60" t="str">
-        <f>VLOOKUP(C75,$H$2:$I$200,2,0)</f>
-        <v>Ecologiste</v>
+        <f>VLOOKUP(C75,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="25">
         <v>2024</v>
       </c>
-      <c r="B76" s="91" t="s">
-        <v>33</v>
+      <c r="B76" s="90" t="s">
+        <v>41</v>
       </c>
       <c r="C76" t="s">
-        <v>134</v>
+        <v>38</v>
+      </c>
+      <c r="D76">
+        <v>72</v>
       </c>
       <c r="E76" s="68">
-        <v>1</v>
+        <f>D76/(D75+D76+D77+D78)</f>
+        <v>0.37305699481865284</v>
       </c>
       <c r="F76" s="60" t="str">
-        <f>VLOOKUP(C76,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C76,$H$2:$I$203,2,0)</f>
+        <v>Gauche Radical</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="25">
         <v>2024</v>
       </c>
-      <c r="B77" s="91" t="s">
-        <v>50</v>
+      <c r="B77" s="90" t="s">
+        <v>41</v>
       </c>
       <c r="C77" t="s">
         <v>134</v>
       </c>
+      <c r="D77">
+        <v>66</v>
+      </c>
       <c r="E77" s="68">
-        <v>1</v>
+        <f>D77/(D75+D76+D77+D78)</f>
+        <v>0.34196891191709844</v>
       </c>
       <c r="F77" s="60" t="str">
-        <f>VLOOKUP(C77,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C77,$H$2:$I$203,2,0)</f>
         <v>Gauche Modéré</v>
       </c>
     </row>
@@ -14502,108 +14514,112 @@
       <c r="A78" s="25">
         <v>2024</v>
       </c>
-      <c r="B78" s="91" t="s">
-        <v>43</v>
+      <c r="B78" s="90" t="s">
+        <v>41</v>
       </c>
       <c r="C78" t="s">
-        <v>134</v>
+        <v>131</v>
+      </c>
+      <c r="D78">
+        <v>38</v>
       </c>
       <c r="E78" s="68">
-        <v>1</v>
+        <f>D78/(D75+D76+D77+D78)</f>
+        <v>0.19689119170984457</v>
       </c>
       <c r="F78" s="60" t="str">
-        <f>VLOOKUP(C78,$H$2:$I$200,2,0)</f>
-        <v>Gauche Modéré</v>
+        <f>VLOOKUP(C78,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="25">
         <v>2024</v>
       </c>
-      <c r="B79" s="92" t="s">
-        <v>14</v>
+      <c r="B79" s="91" t="s">
+        <v>33</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E79" s="68">
         <v>1</v>
       </c>
       <c r="F79" s="60" t="str">
-        <f>VLOOKUP(C79,$H$2:$I$200,2,0)</f>
-        <v>Ecologiste</v>
+        <f>VLOOKUP(C79,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="25">
         <v>2024</v>
       </c>
-      <c r="B80" s="92" t="s">
-        <v>51</v>
+      <c r="B80" s="91" t="s">
+        <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E80" s="68">
         <v>1</v>
       </c>
       <c r="F80" s="60" t="str">
-        <f>VLOOKUP(C80,$H$2:$I$200,2,0)</f>
-        <v>Ecologiste</v>
+        <f>VLOOKUP(C80,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="25">
         <v>2024</v>
       </c>
-      <c r="B81" s="93" t="s">
-        <v>36</v>
+      <c r="B81" s="91" t="s">
+        <v>43</v>
       </c>
       <c r="C81" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E81" s="68">
         <v>1</v>
       </c>
       <c r="F81" s="60" t="str">
-        <f>VLOOKUP(C81,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C81,$H$2:$I$203,2,0)</f>
+        <v>Gauche Modéré</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="25">
         <v>2024</v>
       </c>
-      <c r="B82" s="93" t="s">
-        <v>44</v>
+      <c r="B82" s="92" t="s">
+        <v>14</v>
       </c>
       <c r="C82" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E82" s="68">
         <v>1</v>
       </c>
       <c r="F82" s="60" t="str">
-        <f>VLOOKUP(C82,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C82,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="25">
         <v>2024</v>
       </c>
-      <c r="B83" s="93" t="s">
-        <v>45</v>
+      <c r="B83" s="92" t="s">
+        <v>51</v>
       </c>
       <c r="C83" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="E83" s="68">
         <v>1</v>
       </c>
       <c r="F83" s="60" t="str">
-        <f>VLOOKUP(C83,$H$2:$I$200,2,0)</f>
-        <v>Centre</v>
+        <f>VLOOKUP(C83,$H$2:$I$203,2,0)</f>
+        <v>Ecologiste</v>
       </c>
     </row>
     <row r="84">
@@ -14611,7 +14627,7 @@
         <v>2024</v>
       </c>
       <c r="B84" s="93" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C84" t="s">
         <v>136</v>
@@ -14620,7 +14636,7 @@
         <v>1</v>
       </c>
       <c r="F84" s="60" t="str">
-        <f>VLOOKUP(C84,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C84,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -14629,7 +14645,7 @@
         <v>2024</v>
       </c>
       <c r="B85" s="93" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C85" t="s">
         <v>136</v>
@@ -14638,7 +14654,7 @@
         <v>1</v>
       </c>
       <c r="F85" s="60" t="str">
-        <f>VLOOKUP(C85,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C85,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -14647,7 +14663,7 @@
         <v>2024</v>
       </c>
       <c r="B86" s="93" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C86" t="s">
         <v>136</v>
@@ -14656,7 +14672,7 @@
         <v>1</v>
       </c>
       <c r="F86" s="60" t="str">
-        <f>VLOOKUP(C86,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C86,$H$2:$I$203,2,0)</f>
         <v>Centre</v>
       </c>
     </row>
@@ -14664,90 +14680,90 @@
       <c r="A87" s="25">
         <v>2024</v>
       </c>
-      <c r="B87" s="94" t="s">
-        <v>31</v>
+      <c r="B87" s="93" t="s">
+        <v>46</v>
       </c>
       <c r="C87" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E87" s="68">
         <v>1</v>
       </c>
       <c r="F87" s="60" t="str">
-        <f>VLOOKUP(C87,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C87,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="25">
         <v>2024</v>
       </c>
-      <c r="B88" s="94" t="s">
-        <v>26</v>
+      <c r="B88" s="93" t="s">
+        <v>47</v>
       </c>
       <c r="C88" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E88" s="68">
         <v>1</v>
       </c>
       <c r="F88" s="60" t="str">
-        <f>VLOOKUP(C88,$H$2:$I$200,2,0)</f>
-        <v>Droite</v>
+        <f>VLOOKUP(C88,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="25">
         <v>2024</v>
       </c>
-      <c r="B89" s="95" t="s">
-        <v>37</v>
+      <c r="B89" s="93" t="s">
+        <v>35</v>
       </c>
       <c r="C89" t="s">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="E89" s="68">
         <v>1</v>
       </c>
       <c r="F89" s="60" t="str">
-        <f>VLOOKUP(C89,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C89,$H$2:$I$203,2,0)</f>
+        <v>Centre</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="25">
         <v>2024</v>
       </c>
-      <c r="B90" s="95" t="s">
-        <v>42</v>
+      <c r="B90" s="94" t="s">
+        <v>31</v>
       </c>
       <c r="C90" t="s">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="E90" s="68">
         <v>1</v>
       </c>
       <c r="F90" s="60" t="str">
-        <f>VLOOKUP(C90,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C90,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="25">
         <v>2024</v>
       </c>
-      <c r="B91" s="95" t="s">
-        <v>39</v>
+      <c r="B91" s="94" t="s">
+        <v>26</v>
       </c>
       <c r="C91" t="s">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="E91" s="68">
         <v>1</v>
       </c>
       <c r="F91" s="60" t="str">
-        <f>VLOOKUP(C91,$H$2:$I$200,2,0)</f>
-        <v>Extrème Droite</v>
+        <f>VLOOKUP(C91,$H$2:$I$203,2,0)</f>
+        <v>Droite</v>
       </c>
     </row>
     <row r="92">
@@ -14755,7 +14771,7 @@
         <v>2024</v>
       </c>
       <c r="B92" s="95" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C92" t="s">
         <v>259</v>
@@ -14764,26 +14780,80 @@
         <v>1</v>
       </c>
       <c r="F92" s="60" t="str">
-        <f>VLOOKUP(C92,$H$2:$I$200,2,0)</f>
+        <f>VLOOKUP(C92,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="27">
+      <c r="A93" s="25">
         <v>2024</v>
       </c>
-      <c r="B93" s="96" t="s">
+      <c r="B93" s="95" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>259</v>
+      </c>
+      <c r="E93" s="68">
+        <v>1</v>
+      </c>
+      <c r="F93" s="60" t="str">
+        <f>VLOOKUP(C93,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="25">
+        <v>2024</v>
+      </c>
+      <c r="B94" s="95" t="s">
+        <v>39</v>
+      </c>
+      <c r="C94" t="s">
+        <v>259</v>
+      </c>
+      <c r="E94" s="68">
+        <v>1</v>
+      </c>
+      <c r="F94" s="60" t="str">
+        <f>VLOOKUP(C94,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="25">
+        <v>2024</v>
+      </c>
+      <c r="B95" s="95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" t="s">
+        <v>259</v>
+      </c>
+      <c r="E95" s="68">
+        <v>1</v>
+      </c>
+      <c r="F95" s="60" t="str">
+        <f>VLOOKUP(C95,$H$2:$I$203,2,0)</f>
+        <v>Extrème Droite</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="27">
+        <v>2024</v>
+      </c>
+      <c r="B96" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="C93" s="28" t="s">
+      <c r="C96" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="D93" s="28"/>
-      <c r="E93" s="67">
+      <c r="D96" s="28"/>
+      <c r="E96" s="67">
         <v>1</v>
       </c>
-      <c r="F93" s="60" t="str">
-        <f>VLOOKUP(C93,$H$2:$I$200,2,0)</f>
+      <c r="F96" s="60" t="str">
+        <f>VLOOKUP(C96,$H$2:$I$203,2,0)</f>
         <v>Extrème Droite</v>
       </c>
     </row>

--- a/Data_Election.xlsx
+++ b/Data_Election.xlsx
@@ -9,11 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682" activeTab="1"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Nuances" sheetId="8" r:id="rId10"/>
+    <sheet name="Nuances" sheetId="10" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -1053,6 +1053,171 @@
   <si>
     <t>Bloc</t>
   </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>Règle Générale</t>
+  </si>
+  <si>
+    <t>Pour les PRES, on saisit directement la brique dans la colonne NuancePCF, LFI, PS, EELV, RN, LR, LREM...</t>
+  </si>
+  <si>
+    <t>Pour les PRES, on saisit directement la brique dans la colonne Nuance : PCF, LFI, PS, EELV, RN, LR, LREM...</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> si un candidat représente une alliance, on crée une nuance composite avec prorata Voir tableau 3</t>
+  </si>
+  <si>
+    <t>Règle Générale PRES</t>
+  </si>
+  <si>
+    <t>On saisit directement la brique dans la colonne Nuance : PCF, LFI, PS, EELV, RN, LR, LREM...</t>
+  </si>
+  <si>
+    <t>Alliance Composite PRES et LEG</t>
+  </si>
+  <si>
+    <t>Scrutin</t>
+  </si>
+  <si>
+    <t>Candidat/Alliance</t>
+  </si>
+  <si>
+    <t>Poid</t>
+  </si>
+  <si>
+    <t>Source du Poid</t>
+  </si>
+  <si>
+    <t>Melenchon (PCF+LFI)</t>
+  </si>
+  <si>
+    <t>Candidat</t>
+  </si>
+  <si>
+    <t>Alliance</t>
+  </si>
+  <si>
+    <t>Melenchon</t>
+  </si>
+  <si>
+    <t>Règle Générale PRES pour la Gauche</t>
+  </si>
+  <si>
+    <t>Joly</t>
+  </si>
+  <si>
+    <t>Holland</t>
+  </si>
+  <si>
+    <t>Hamon</t>
+  </si>
+  <si>
+    <t>Nuance Officiel</t>
+  </si>
+  <si>
+    <t>Nuance crée</t>
+  </si>
+  <si>
+    <t>Roussel</t>
+  </si>
+  <si>
+    <t>Hidalgo</t>
+  </si>
+  <si>
+    <t>Jadot</t>
+  </si>
+  <si>
+    <t>Poids</t>
+  </si>
+  <si>
+    <t>Nuances permanentes — Année = 0 (valables pour toutes les élections)</t>
+  </si>
+  <si>
+    <t>Nuance permanente — extrême gauche</t>
+  </si>
+  <si>
+    <t>Nuance permanente</t>
+  </si>
+  <si>
+    <t>Nuance permanente — quand FI seul (LEG)</t>
+  </si>
+  <si>
+    <t>Convention : PRG satellite PS</t>
+  </si>
+  <si>
+    <t>Convention : divers gauche → PS</t>
+  </si>
+  <si>
+    <t>Nuance permanente — La République En Marche</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Ensemble</t>
+  </si>
+  <si>
+    <t>Nuance permanente — MoDem</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Horizons</t>
+  </si>
+  <si>
+    <t>Nuance permanente — divers centre</t>
+  </si>
+  <si>
+    <t>Nuance permanente — majorité présidentielle</t>
+  </si>
+  <si>
+    <t>Nuance permanente — divers droite</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Debout la France</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Front National</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Rassemblement National (ex FN)</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Reconquête</t>
+  </si>
+  <si>
+    <t>Nuance permanente — Mouvement Pour la France</t>
+  </si>
+  <si>
+    <t>Alliances composites — Année spécifique + prorata élus AN</t>
+  </si>
+  <si>
+    <t>FG 2012 (PRES Mélenchon + LEG) — prorata élus GDR 2007 : 15 PCF / 15 DVG filiation LFI</t>
+  </si>
+  <si>
+    <t>FG 2012 — idem</t>
+  </si>
+  <si>
+    <t>FG 2017 PRES uniquement — prorata élus GDR 2012 : 16 PCF / 17 DVG filiation LFI</t>
+  </si>
+  <si>
+    <t>FG 2017 — idem</t>
+  </si>
+  <si>
+    <t>NG 2017 PRES Hamon — prorata groupe Nouvelle Gauche AN 2017 : 28 PS / 3 EELV</t>
+  </si>
+  <si>
+    <t>NG 2017 — idem</t>
+  </si>
+  <si>
+    <t>NUPES 2022 LEG — prorata élus AN 2024 : PCF 22 / LFI 75 / PS 64 / EELV 23</t>
+  </si>
+  <si>
+    <t>NUPES 2022 — idem</t>
+  </si>
+  <si>
+    <t>NFP 2024 LEG — prorata élus AN 2024 : PCF 17 / LFI 72 / PS 66 / EELV 38</t>
+  </si>
+  <si>
+    <t>NFP 2024 — idem</t>
+  </si>
 </sst>
 </file>
 
@@ -1065,7 +1230,7 @@
     <numFmt numFmtId="167" formatCode="0.0000"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1232,8 +1397,76 @@
       <name val="Segoe UI"/>
       <color rgb="FF000000"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <color rgb="FFFFFFFF"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FF888888"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color theme="1"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <color rgb="FF555555"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <charset val="1"/>
+      <family val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="27">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1305,8 +1538,80 @@
         <fgColor rgb="FF9BBB59"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF404040"/>
+        <bgColor rgb="FF555555"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF555555"/>
+        <bgColor rgb="FF404040"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8B0000"/>
+        <bgColor rgb="FF800000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC0000"/>
+        <bgColor rgb="FF8B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4444"/>
+        <bgColor rgb="FF993366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8A080"/>
+        <bgColor rgb="FFFF99CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CAF50"/>
+        <bgColor rgb="FF888888"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDD835"/>
+        <bgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF42A5F5"/>
+        <bgColor rgb="FF00CCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A237E"/>
+        <bgColor rgb="FF333399"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9C4"/>
+        <bgColor rgb="FFFFFF99"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1589,11 +1894,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" xfId="0"/>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="3" applyFill="1" xfId="0"/>
@@ -1715,6 +2058,110 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="27" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="26" applyFont="1" fillId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="28" applyBorder="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="29" applyBorder="1" applyAlignment="1" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="2" applyFill="1" borderId="30" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="27" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="15" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="29" applyFont="1" fillId="16" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="30" applyFont="1" fillId="17" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="18" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="31" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="32" applyFont="1" fillId="0" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment wrapText="1" vertical="center" horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="19" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="20" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="21" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="22" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="23" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="24" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="25" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="33" applyFont="1" fillId="26" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="28" applyFont="1" fillId="19" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="26" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="168" applyNumberFormat="1" fontId="31" applyFont="1" fillId="0" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="0" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="32" applyFont="1" fillId="0" applyFill="1" borderId="31" applyBorder="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment wrapText="1" vertical="center" horizontal="left"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="33" applyFont="1" fillId="26" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="31" applyFont="1" fillId="26" applyFill="1" applyAlignment="1" applyProtection="1" xfId="0">
+      <alignment vertical="center" horizontal="center"/>
+      <protection/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5165,7 +5612,7 @@
         <v>36054394</v>
       </c>
       <c r="J87" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="K87">
         <v>2291288</v>
@@ -5669,7 +6116,7 @@
         <v>139577</v>
       </c>
       <c r="J101" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="K101">
         <v>7435</v>
@@ -8192,7 +8639,7 @@
         <v>35132947</v>
       </c>
       <c r="J171" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K171">
         <v>7712520</v>
@@ -8303,7 +8750,7 @@
         <v>35132947</v>
       </c>
       <c r="J174" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K174">
         <v>1627853</v>
@@ -8377,7 +8824,7 @@
         <v>35132947</v>
       </c>
       <c r="J176" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="K176">
         <v>802422</v>
@@ -8451,7 +8898,7 @@
         <v>35132947</v>
       </c>
       <c r="J178" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="K178">
         <v>616478</v>
@@ -8710,7 +9157,7 @@
         <v>139655</v>
       </c>
       <c r="J185" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K185">
         <v>24332</v>
@@ -8858,7 +9305,7 @@
         <v>139655</v>
       </c>
       <c r="J189" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K189">
         <v>5796</v>
@@ -8895,7 +9342,7 @@
         <v>139655</v>
       </c>
       <c r="J190" t="s">
-        <v>157</v>
+        <v>40</v>
       </c>
       <c r="K190">
         <v>3493</v>
@@ -8969,7 +9416,7 @@
         <v>139655</v>
       </c>
       <c r="J192" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="K192">
         <v>2491</v>
@@ -9302,7 +9749,7 @@
         <v>22744708</v>
       </c>
       <c r="J201" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K201">
         <v>608314</v>
@@ -10375,7 +10822,7 @@
         <v>52395</v>
       </c>
       <c r="J230" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K230">
         <v>1283</v>
@@ -10412,7 +10859,7 @@
         <v>52395</v>
       </c>
       <c r="J231" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="K231">
         <v>663</v>
@@ -10745,7 +11192,7 @@
         <v>41266</v>
       </c>
       <c r="J240" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="K240">
         <v>856</v>
@@ -10782,7 +11229,7 @@
         <v>41266</v>
       </c>
       <c r="J241" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="K241">
         <v>578</v>
@@ -12976,1888 +13423,1162 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" defaultColWidth="8.6796875"/>
   <cols>
-    <col min="2" max="2" width="9.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.453125" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" width="7" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" width="23.1796875" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" width="18.1796875" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" width="20.453125" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" width="20.453125" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="8" customWidth="1" style="117"/>
+    <col min="2" max="2" width="10" customWidth="1" style="117"/>
+    <col min="3" max="3" width="18" customWidth="1" style="117"/>
+    <col min="4" max="4" width="8" customWidth="1" style="117"/>
+    <col min="5" max="5" width="10" customWidth="1" style="117"/>
+    <col min="6" max="6" width="22" customWidth="1" style="117"/>
+    <col min="7" max="7" width="50" customWidth="1" style="117"/>
+    <col min="8" max="16384" width="8.6796875" style="117"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" customHeight="1" ht="21.75">
+      <c r="A1" s="118" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="118" t="s">
         <v>156</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="118" t="s">
         <v>262</v>
       </c>
-      <c r="E1" s="66" t="s">
-        <v>264</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="E1" s="118" t="s">
+        <v>301</v>
+      </c>
+      <c r="F1" s="118" t="s">
         <v>125</v>
       </c>
-      <c r="H1" t="s">
-        <v>156</v>
-      </c>
-      <c r="I1" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="22">
-        <v>2007</v>
-      </c>
-      <c r="B2" s="109" t="s">
+      <c r="G1" s="118" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" ht="18">
+      <c r="A2" s="119" t="s">
+        <v>302</v>
+      </c>
+      <c r="B2" s="119"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+    </row>
+    <row r="3" customHeight="1" ht="15.75">
+      <c r="A3" s="120">
+        <v>0</v>
+      </c>
+      <c r="B3" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C3" s="121" t="s">
         <v>273</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="66">
+      <c r="D3" s="122"/>
+      <c r="E3" s="123">
         <v>1</v>
       </c>
-      <c r="F2" s="60" t="str">
-        <f>VLOOKUP(C2,$H$2:$I$203,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F3" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="G3" s="125" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" ht="15.75">
+      <c r="A4" s="120">
+        <v>0</v>
+      </c>
+      <c r="B4" s="121" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="121" t="s">
         <v>273</v>
       </c>
-      <c r="I2" t="s">
+      <c r="D4" s="122"/>
+      <c r="E4" s="123">
+        <v>1</v>
+      </c>
+      <c r="F4" s="124" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="G4" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" ht="15.75">
+      <c r="A5" s="120">
+        <v>0</v>
+      </c>
+      <c r="B5" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="D3">
+      <c r="D5" s="122"/>
+      <c r="E5" s="123">
+        <v>1</v>
+      </c>
+      <c r="F5" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G5" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" ht="15.75">
+      <c r="A6" s="120">
+        <v>0</v>
+      </c>
+      <c r="B6" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="122"/>
+      <c r="E6" s="123">
+        <v>1</v>
+      </c>
+      <c r="F6" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="125" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" ht="15.75">
+      <c r="A7" s="120">
+        <v>0</v>
+      </c>
+      <c r="B7" s="128" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="128" t="s">
+        <v>134</v>
+      </c>
+      <c r="D7" s="122"/>
+      <c r="E7" s="123">
+        <v>1</v>
+      </c>
+      <c r="F7" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" ht="15.75">
+      <c r="A8" s="120">
+        <v>0</v>
+      </c>
+      <c r="B8" s="128" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="122"/>
+      <c r="E8" s="123">
+        <v>1</v>
+      </c>
+      <c r="F8" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="125" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" ht="15.75">
+      <c r="A9" s="120">
+        <v>0</v>
+      </c>
+      <c r="B9" s="128" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="128" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="122"/>
+      <c r="E9" s="123">
+        <v>1</v>
+      </c>
+      <c r="F9" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="125" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" ht="15.75">
+      <c r="A10" s="120">
+        <v>0</v>
+      </c>
+      <c r="B10" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D10" s="122"/>
+      <c r="E10" s="123">
+        <v>1</v>
+      </c>
+      <c r="F10" s="124" t="s">
+        <v>130</v>
+      </c>
+      <c r="G10" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" ht="15.75">
+      <c r="A11" s="120">
+        <v>0</v>
+      </c>
+      <c r="B11" s="129" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="122"/>
+      <c r="E11" s="123">
+        <v>1</v>
+      </c>
+      <c r="F11" s="124" t="s">
+        <v>130</v>
+      </c>
+      <c r="G11" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" ht="15.75">
+      <c r="A12" s="120">
+        <v>0</v>
+      </c>
+      <c r="B12" s="130" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="122"/>
+      <c r="E12" s="123">
+        <v>1</v>
+      </c>
+      <c r="F12" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" ht="15.75">
+      <c r="A13" s="120">
+        <v>0</v>
+      </c>
+      <c r="B13" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D13" s="122"/>
+      <c r="E13" s="123">
+        <v>1</v>
+      </c>
+      <c r="F13" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" ht="15.75">
+      <c r="A14" s="120">
+        <v>0</v>
+      </c>
+      <c r="B14" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="68">
+      <c r="C14" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="122"/>
+      <c r="E14" s="123">
         <v>1</v>
       </c>
-      <c r="F3" s="60" t="str">
-        <f>VLOOKUP(C3,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-      <c r="H3" t="s">
+      <c r="F14" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G14" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" ht="15.75">
+      <c r="A15" s="120">
+        <v>0</v>
+      </c>
+      <c r="B15" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D15" s="122"/>
+      <c r="E15" s="123">
+        <v>1</v>
+      </c>
+      <c r="F15" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G15" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" ht="15.75">
+      <c r="A16" s="120">
+        <v>0</v>
+      </c>
+      <c r="B16" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D16" s="122"/>
+      <c r="E16" s="123">
+        <v>1</v>
+      </c>
+      <c r="F16" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G16" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" ht="15.75">
+      <c r="A17" s="120">
+        <v>0</v>
+      </c>
+      <c r="B17" s="130" t="s">
+        <v>85</v>
+      </c>
+      <c r="C17" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D17" s="122"/>
+      <c r="E17" s="123">
+        <v>1</v>
+      </c>
+      <c r="F17" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G17" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" ht="15.75">
+      <c r="A18" s="120">
+        <v>0</v>
+      </c>
+      <c r="B18" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="122"/>
+      <c r="E18" s="123">
+        <v>1</v>
+      </c>
+      <c r="F18" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G18" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" ht="15.75">
+      <c r="A19" s="120">
+        <v>0</v>
+      </c>
+      <c r="B19" s="130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="122"/>
+      <c r="E19" s="123">
+        <v>1</v>
+      </c>
+      <c r="F19" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G19" s="125" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" ht="15.75">
+      <c r="A20" s="120">
+        <v>0</v>
+      </c>
+      <c r="B20" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="122"/>
+      <c r="E20" s="123">
+        <v>1</v>
+      </c>
+      <c r="F20" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G20" s="125" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" ht="15.75">
+      <c r="A21" s="120">
+        <v>0</v>
+      </c>
+      <c r="B21" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="122"/>
+      <c r="E21" s="123">
+        <v>1</v>
+      </c>
+      <c r="F21" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="125" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" ht="15.75">
+      <c r="A22" s="120">
+        <v>0</v>
+      </c>
+      <c r="B22" s="130" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D22" s="122"/>
+      <c r="E22" s="123">
+        <v>1</v>
+      </c>
+      <c r="F22" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" ht="15.75">
+      <c r="A23" s="120">
+        <v>0</v>
+      </c>
+      <c r="B23" s="130" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="122"/>
+      <c r="E23" s="123">
+        <v>1</v>
+      </c>
+      <c r="F23" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="125" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" ht="15.75">
+      <c r="A24" s="120">
+        <v>0</v>
+      </c>
+      <c r="B24" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="122"/>
+      <c r="E24" s="123">
+        <v>1</v>
+      </c>
+      <c r="F24" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G24" s="125" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" ht="15.75">
+      <c r="A25" s="120">
+        <v>0</v>
+      </c>
+      <c r="B25" s="130" t="s">
+        <v>242</v>
+      </c>
+      <c r="C25" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="122"/>
+      <c r="E25" s="123">
+        <v>1</v>
+      </c>
+      <c r="F25" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" ht="15.75">
+      <c r="A26" s="120">
+        <v>0</v>
+      </c>
+      <c r="B26" s="130" t="s">
+        <v>243</v>
+      </c>
+      <c r="C26" s="130" t="s">
+        <v>136</v>
+      </c>
+      <c r="D26" s="122"/>
+      <c r="E26" s="123">
+        <v>1</v>
+      </c>
+      <c r="F26" s="124" t="s">
+        <v>136</v>
+      </c>
+      <c r="G26" s="125" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" ht="15.75">
+      <c r="A27" s="120">
+        <v>0</v>
+      </c>
+      <c r="B27" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="131" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="122"/>
+      <c r="E27" s="123">
+        <v>1</v>
+      </c>
+      <c r="F27" s="124" t="s">
+        <v>138</v>
+      </c>
+      <c r="G27" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" ht="15.75">
+      <c r="A28" s="120">
+        <v>0</v>
+      </c>
+      <c r="B28" s="131" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="131" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="122"/>
+      <c r="E28" s="123">
+        <v>1</v>
+      </c>
+      <c r="F28" s="124" t="s">
+        <v>138</v>
+      </c>
+      <c r="G28" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" ht="15.75">
+      <c r="A29" s="120">
+        <v>0</v>
+      </c>
+      <c r="B29" s="131" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="131" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29" s="122"/>
+      <c r="E29" s="123">
+        <v>1</v>
+      </c>
+      <c r="F29" s="124" t="s">
+        <v>138</v>
+      </c>
+      <c r="G29" s="125" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" ht="15.75">
+      <c r="A30" s="120">
+        <v>0</v>
+      </c>
+      <c r="B30" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C30" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D30" s="122"/>
+      <c r="E30" s="123">
+        <v>1</v>
+      </c>
+      <c r="F30" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G30" s="125" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" ht="15.75">
+      <c r="A31" s="120">
+        <v>0</v>
+      </c>
+      <c r="B31" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="C31" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="122"/>
+      <c r="E31" s="123">
+        <v>1</v>
+      </c>
+      <c r="F31" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G31" s="125" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" ht="15.75">
+      <c r="A32" s="120">
+        <v>0</v>
+      </c>
+      <c r="B32" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D32" s="122"/>
+      <c r="E32" s="123">
+        <v>1</v>
+      </c>
+      <c r="F32" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G32" s="125" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" ht="15.75">
+      <c r="A33" s="120">
+        <v>0</v>
+      </c>
+      <c r="B33" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="C33" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D33" s="122"/>
+      <c r="E33" s="123">
+        <v>1</v>
+      </c>
+      <c r="F33" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G33" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" ht="15.75">
+      <c r="A34" s="120">
+        <v>0</v>
+      </c>
+      <c r="B34" s="132" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D34" s="122"/>
+      <c r="E34" s="123">
+        <v>1</v>
+      </c>
+      <c r="F34" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G34" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" ht="15.75">
+      <c r="A35" s="120">
+        <v>0</v>
+      </c>
+      <c r="B35" s="132" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D35" s="122"/>
+      <c r="E35" s="123">
+        <v>1</v>
+      </c>
+      <c r="F35" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G35" s="125" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" ht="15.75">
+      <c r="A36" s="120">
+        <v>0</v>
+      </c>
+      <c r="B36" s="132" t="s">
+        <v>48</v>
+      </c>
+      <c r="C36" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="122"/>
+      <c r="E36" s="123">
+        <v>1</v>
+      </c>
+      <c r="F36" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G36" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" ht="15.75">
+      <c r="A37" s="120">
+        <v>0</v>
+      </c>
+      <c r="B37" s="132" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D37" s="122"/>
+      <c r="E37" s="123">
+        <v>1</v>
+      </c>
+      <c r="F37" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G37" s="125" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" ht="15.75">
+      <c r="A38" s="120">
+        <v>0</v>
+      </c>
+      <c r="B38" s="132" t="s">
+        <v>244</v>
+      </c>
+      <c r="C38" s="132" t="s">
+        <v>227</v>
+      </c>
+      <c r="D38" s="122"/>
+      <c r="E38" s="123">
+        <v>1</v>
+      </c>
+      <c r="F38" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="G38" s="125" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" ht="18">
+      <c r="A39" s="119" t="s">
+        <v>320</v>
+      </c>
+      <c r="B39" s="119"/>
+      <c r="C39" s="119"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="119"/>
+    </row>
+    <row r="40" ht="23.25">
+      <c r="A40" s="133">
+        <v>2012</v>
+      </c>
+      <c r="B40" s="134" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="134" t="s">
         <v>157</v>
       </c>
-      <c r="I3" t="s">
+      <c r="D40" s="135">
+        <v>7</v>
+      </c>
+      <c r="E40" s="136">
+        <f>D40/(D40+D41)</f>
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="F40" s="137" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B4" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="G40" s="138" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="139">
+        <v>2012</v>
+      </c>
+      <c r="B41" s="127" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="140">
+        <v>8</v>
+      </c>
+      <c r="E41" s="123">
+        <f>D41/(D40+D41)</f>
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="F41" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G41" s="125" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" ht="23.25">
+      <c r="A42" s="133">
+        <v>2017</v>
+      </c>
+      <c r="B42" s="134" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="135">
+        <v>16</v>
+      </c>
+      <c r="E42" s="136">
+        <f>D42/(D42+D43)</f>
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="F42" s="137" t="s">
+        <v>126</v>
+      </c>
+      <c r="G42" s="138" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="139">
+        <v>2017</v>
+      </c>
+      <c r="B43" s="127" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="140">
+        <v>17</v>
+      </c>
+      <c r="E43" s="123">
+        <f>D43/(D42+D43)</f>
+        <v>0.5151515151515151</v>
+      </c>
+      <c r="F43" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G43" s="125" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="44" ht="23.25">
+      <c r="A44" s="139">
+        <v>2017</v>
+      </c>
+      <c r="B44" s="128" t="s">
+        <v>276</v>
+      </c>
+      <c r="C44" s="128" t="s">
         <v>134</v>
       </c>
-      <c r="E4" s="68">
-        <v>1</v>
-      </c>
-      <c r="F4" s="60" t="str">
-        <f>VLOOKUP(C4,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="D44" s="140">
+        <v>28</v>
+      </c>
+      <c r="E44" s="123">
+        <f>D44/(D44+D45)</f>
+        <v>0.9032258064516129</v>
+      </c>
+      <c r="F44" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" s="125" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="139">
+        <v>2017</v>
+      </c>
+      <c r="B45" s="129" t="s">
+        <v>276</v>
+      </c>
+      <c r="C45" s="129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="140">
+        <v>3</v>
+      </c>
+      <c r="E45" s="123">
+        <f>D45/(D44+D45)</f>
+        <v>9.67741935483871E-2</v>
+      </c>
+      <c r="F45" s="124" t="s">
+        <v>130</v>
+      </c>
+      <c r="G45" s="125" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="46" ht="23.25">
+      <c r="A46" s="133">
+        <v>2022</v>
+      </c>
+      <c r="B46" s="134" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="135">
+        <v>22</v>
+      </c>
+      <c r="E46" s="136">
+        <f>D46/(D46+D47+D48+D49)</f>
+        <v>0.11956521739130435</v>
+      </c>
+      <c r="F46" s="137" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="138" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="139">
+        <v>2022</v>
+      </c>
+      <c r="B47" s="127" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="I4" t="s">
+      <c r="D47" s="140">
+        <v>75</v>
+      </c>
+      <c r="E47" s="123">
+        <f>D47/(D46+D47+D48+D49)</f>
+        <v>0.4076086956521739</v>
+      </c>
+      <c r="F47" s="124" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B5" s="75" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="G47" s="125" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="139">
+        <v>2022</v>
+      </c>
+      <c r="B48" s="128" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="128" t="s">
         <v>134</v>
       </c>
-      <c r="D5">
-        <v>186</v>
-      </c>
-      <c r="E5" s="68">
-        <v>1</v>
-      </c>
-      <c r="F5" s="60" t="str">
-        <f>VLOOKUP(C5,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="D48" s="140">
+        <v>64</v>
+      </c>
+      <c r="E48" s="123">
+        <f>D48/(D46+D47+D48+D49)</f>
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="F48" s="124" t="s">
+        <v>133</v>
+      </c>
+      <c r="G48" s="125" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" ht="15.75">
+      <c r="A49" s="139">
+        <v>2022</v>
+      </c>
+      <c r="B49" s="129" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" s="129" t="s">
+        <v>131</v>
+      </c>
+      <c r="D49" s="140">
+        <v>23</v>
+      </c>
+      <c r="E49" s="123">
+        <f>D49/(D46+D47+D48+D49)</f>
+        <v>0.125</v>
+      </c>
+      <c r="F49" s="124" t="s">
+        <v>130</v>
+      </c>
+      <c r="G49" s="125" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="50" ht="23.25">
+      <c r="A50" s="133">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="134" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="134" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" s="135">
+        <v>17</v>
+      </c>
+      <c r="E50" s="136">
+        <f>D50/(D50+D51+D52+D53)</f>
+        <v>8.808290155440414E-2</v>
+      </c>
+      <c r="F50" s="137" t="s">
+        <v>126</v>
+      </c>
+      <c r="G50" s="138" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" ht="15.75">
+      <c r="A51" s="139">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="127" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="127" t="s">
+        <v>38</v>
+      </c>
+      <c r="D51" s="140">
+        <v>72</v>
+      </c>
+      <c r="E51" s="123">
+        <f>D51/(D50+D51+D52+D53)</f>
+        <v>0.37305699481865284</v>
+      </c>
+      <c r="F51" s="124" t="s">
+        <v>126</v>
+      </c>
+      <c r="G51" s="125" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" ht="15.75">
+      <c r="A52" s="139">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="128" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="128" t="s">
         <v>134</v>
       </c>
-      <c r="I5" t="s">
+      <c r="D52" s="140">
+        <v>66</v>
+      </c>
+      <c r="E52" s="123">
+        <f>D52/(D50+D51+D52+D53)</f>
+        <v>0.34196891191709844</v>
+      </c>
+      <c r="F52" s="124" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B6" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6" s="68">
-        <v>1</v>
-      </c>
-      <c r="F6" s="60" t="str">
-        <f>VLOOKUP(C6,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="G52" s="125" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="139">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="129" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="129" t="s">
         <v>131</v>
       </c>
-      <c r="I6" t="s">
+      <c r="D53" s="140">
+        <v>38</v>
+      </c>
+      <c r="E53" s="123">
+        <f>D53/(D50+D51+D52+D53)</f>
+        <v>0.19689119170984457</v>
+      </c>
+      <c r="F53" s="124" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B7" s="70" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7">
-        <v>18</v>
-      </c>
-      <c r="E7" s="68">
-        <v>1</v>
-      </c>
-      <c r="F7" s="60" t="str">
-        <f>VLOOKUP(C7,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-      <c r="H7" t="s">
-        <v>136</v>
-      </c>
-      <c r="I7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" s="68">
-        <v>1</v>
-      </c>
-      <c r="F8" s="60" t="str">
-        <f>VLOOKUP(C8,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-      <c r="H8" t="s">
-        <v>138</v>
-      </c>
-      <c r="I8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="C9" t="s">
-        <v>136</v>
-      </c>
-      <c r="E9" s="68">
-        <v>1</v>
-      </c>
-      <c r="F9" s="60" t="str">
-        <f>VLOOKUP(C9,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-      <c r="H9" t="s">
-        <v>259</v>
-      </c>
-      <c r="I9" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" t="s">
-        <v>136</v>
-      </c>
-      <c r="E10" s="68">
-        <v>1</v>
-      </c>
-      <c r="F10" s="60" t="str">
-        <f>VLOOKUP(C10,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="68">
-        <v>1</v>
-      </c>
-      <c r="F11" s="60" t="str">
-        <f>VLOOKUP(C11,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E12" s="68">
-        <v>1</v>
-      </c>
-      <c r="F12" s="60" t="str">
-        <f>VLOOKUP(C12,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="25">
-        <v>2007</v>
-      </c>
-      <c r="B13" s="80" t="s">
-        <v>244</v>
-      </c>
-      <c r="C13" t="s">
-        <v>259</v>
-      </c>
-      <c r="E13" s="68">
-        <v>1</v>
-      </c>
-      <c r="F13" s="60" t="str">
-        <f>VLOOKUP(C13,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="27">
-        <v>2007</v>
-      </c>
-      <c r="B14" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="68">
-        <v>1</v>
-      </c>
-      <c r="F14" s="60" t="str">
-        <f>VLOOKUP(C14,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22">
-        <v>2012</v>
-      </c>
-      <c r="B15" s="109" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="66">
-        <v>1</v>
-      </c>
-      <c r="F15" s="60" t="str">
-        <f>VLOOKUP(C15,$H$2:$I$203,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B16" s="90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>157</v>
-      </c>
-      <c r="D16">
-        <v>7</v>
-      </c>
-      <c r="E16" s="68">
-        <f>D16/(D16+D17)</f>
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="F16" s="60" t="str">
-        <f>VLOOKUP(C16,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B17" s="90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17">
-        <v>8</v>
-      </c>
-      <c r="E17" s="68">
-        <f>D17/(D16+D17)</f>
-        <v>0.5333333333333333</v>
-      </c>
-      <c r="F17" s="60" t="str">
-        <f>VLOOKUP(C17,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B18" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>134</v>
-      </c>
-      <c r="D18">
-        <v>295</v>
-      </c>
-      <c r="E18" s="68">
-        <v>1</v>
-      </c>
-      <c r="F18" s="60" t="str">
-        <f>VLOOKUP(C18,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B19" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" t="s">
-        <v>134</v>
-      </c>
-      <c r="E19" s="68">
-        <v>1</v>
-      </c>
-      <c r="F19" s="60" t="str">
-        <f>VLOOKUP(C19,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B20" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>134</v>
-      </c>
-      <c r="E20" s="68">
-        <v>1</v>
-      </c>
-      <c r="F20" s="60" t="str">
-        <f>VLOOKUP(C20,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B21" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" t="s">
-        <v>131</v>
-      </c>
-      <c r="D21">
-        <v>18</v>
-      </c>
-      <c r="E21" s="68">
-        <v>1</v>
-      </c>
-      <c r="F21" s="60" t="str">
-        <f>VLOOKUP(C21,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B22" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" t="s">
-        <v>131</v>
-      </c>
-      <c r="E22" s="68">
-        <v>1</v>
-      </c>
-      <c r="F22" s="60" t="str">
-        <f>VLOOKUP(C22,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B23" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="C23" t="s">
-        <v>136</v>
-      </c>
-      <c r="E23" s="68">
-        <v>1</v>
-      </c>
-      <c r="F23" s="60" t="str">
-        <f>VLOOKUP(C23,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B24" s="93" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" t="s">
-        <v>136</v>
-      </c>
-      <c r="E24" s="68">
-        <v>1</v>
-      </c>
-      <c r="F24" s="60" t="str">
-        <f>VLOOKUP(C24,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B25" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>136</v>
-      </c>
-      <c r="E25" s="68">
-        <v>1</v>
-      </c>
-      <c r="F25" s="60" t="str">
-        <f>VLOOKUP(C25,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B26" s="93" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E26" s="68">
-        <v>1</v>
-      </c>
-      <c r="F26" s="60" t="str">
-        <f>VLOOKUP(C26,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B27" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>136</v>
-      </c>
-      <c r="E27" s="68">
-        <v>1</v>
-      </c>
-      <c r="F27" s="60" t="str">
-        <f>VLOOKUP(C27,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B28" s="93" t="s">
-        <v>85</v>
-      </c>
-      <c r="C28" t="s">
-        <v>136</v>
-      </c>
-      <c r="E28" s="68">
-        <v>1</v>
-      </c>
-      <c r="F28" s="60" t="str">
-        <f>VLOOKUP(C28,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B29" s="93" t="s">
-        <v>86</v>
-      </c>
-      <c r="C29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" s="68">
-        <v>1</v>
-      </c>
-      <c r="F29" s="60" t="str">
-        <f>VLOOKUP(C29,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B30" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E30" s="68">
-        <v>1</v>
-      </c>
-      <c r="F30" s="60" t="str">
-        <f>VLOOKUP(C30,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B31" s="94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" t="s">
-        <v>138</v>
-      </c>
-      <c r="E31" s="68">
-        <v>1</v>
-      </c>
-      <c r="F31" s="60" t="str">
-        <f>VLOOKUP(C31,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="25">
-        <v>2012</v>
-      </c>
-      <c r="B32" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" t="s">
-        <v>259</v>
-      </c>
-      <c r="E32" s="68">
-        <v>1</v>
-      </c>
-      <c r="F32" s="60" t="str">
-        <f>VLOOKUP(C32,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="27">
-        <v>2012</v>
-      </c>
-      <c r="B33" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D33" s="28"/>
-      <c r="E33" s="68">
-        <v>1</v>
-      </c>
-      <c r="F33" s="60" t="str">
-        <f>VLOOKUP(C33,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34">
-        <v>2017</v>
-      </c>
-      <c r="B34" s="82" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
-        <v>273</v>
-      </c>
-      <c r="D34"/>
-      <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" s="60" t="str">
-        <f>VLOOKUP(C34,$H$2:$I$203,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>2017</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D35"/>
-      <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" s="60" t="str">
-        <f>VLOOKUP(C35,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>2017</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36"/>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36" s="60" t="str">
-        <f>VLOOKUP(C36,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B37" s="90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" t="s">
-        <v>157</v>
-      </c>
-      <c r="D37">
-        <v>16</v>
-      </c>
-      <c r="E37" s="68">
-        <f>D37/(D37+D38)</f>
-        <v>0.48484848484848486</v>
-      </c>
-      <c r="F37" s="60" t="str">
-        <f>VLOOKUP(C37,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B38" s="90" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38">
-        <v>17</v>
-      </c>
-      <c r="E38" s="68">
-        <f>D38/(D37+D38)</f>
-        <v>0.5151515151515151</v>
-      </c>
-      <c r="F38" s="60" t="str">
-        <f>VLOOKUP(C38,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B39" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39">
-        <v>28</v>
-      </c>
-      <c r="E39" s="68">
-        <v>1</v>
-      </c>
-      <c r="F39" s="60" t="str">
-        <f>VLOOKUP(C39,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B40" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="C40" t="s">
-        <v>134</v>
-      </c>
-      <c r="E40" s="68">
-        <v>1</v>
-      </c>
-      <c r="F40" s="60" t="str">
-        <f>VLOOKUP(C40,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B41" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" t="s">
-        <v>134</v>
-      </c>
-      <c r="E41" s="68">
-        <v>1</v>
-      </c>
-      <c r="F41" s="60" t="str">
-        <f>VLOOKUP(C41,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B42" s="97" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" t="s">
-        <v>131</v>
-      </c>
-      <c r="D42">
-        <v>3</v>
-      </c>
-      <c r="E42" s="68">
-        <v>1</v>
-      </c>
-      <c r="F42" s="60" t="str">
-        <f>VLOOKUP(C42,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B43" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C43" t="s">
-        <v>136</v>
-      </c>
-      <c r="E43" s="68">
-        <v>1</v>
-      </c>
-      <c r="F43" s="60" t="str">
-        <f>VLOOKUP(C43,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B44" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>136</v>
-      </c>
-      <c r="E44" s="68">
-        <v>1</v>
-      </c>
-      <c r="F44" s="60" t="str">
-        <f>VLOOKUP(C44,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B45" s="93" t="s">
-        <v>30</v>
-      </c>
-      <c r="C45" t="s">
-        <v>136</v>
-      </c>
-      <c r="E45" s="68">
-        <v>1</v>
-      </c>
-      <c r="F45" s="60" t="str">
-        <f>VLOOKUP(C45,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B46" s="93" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" t="s">
-        <v>136</v>
-      </c>
-      <c r="E46" s="68">
-        <v>1</v>
-      </c>
-      <c r="F46" s="60" t="str">
-        <f>VLOOKUP(C46,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B47" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" t="s">
-        <v>136</v>
-      </c>
-      <c r="E47" s="68">
-        <v>1</v>
-      </c>
-      <c r="F47" s="60" t="str">
-        <f>VLOOKUP(C47,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B48" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="68">
-        <v>1</v>
-      </c>
-      <c r="F48" s="60" t="str">
-        <f>VLOOKUP(C48,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B49" s="94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="68">
-        <v>1</v>
-      </c>
-      <c r="F49" s="60" t="str">
-        <f>VLOOKUP(C49,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B50" s="95" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" t="s">
-        <v>259</v>
-      </c>
-      <c r="E50" s="68">
-        <v>1</v>
-      </c>
-      <c r="F50" s="60" t="str">
-        <f>VLOOKUP(C50,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="25">
-        <v>2017</v>
-      </c>
-      <c r="B51" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" t="s">
-        <v>259</v>
-      </c>
-      <c r="E51" s="68">
-        <v>1</v>
-      </c>
-      <c r="F51" s="60" t="str">
-        <f>VLOOKUP(C51,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="27">
-        <v>2017</v>
-      </c>
-      <c r="B52" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C52" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D52" s="28"/>
-      <c r="E52" s="68">
-        <v>1</v>
-      </c>
-      <c r="F52" s="60" t="str">
-        <f>VLOOKUP(C52,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="22">
-        <v>2022</v>
-      </c>
-      <c r="B53" s="84" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D53" s="23"/>
-      <c r="E53" s="66">
-        <v>1</v>
-      </c>
-      <c r="F53" s="60" t="str">
-        <f>VLOOKUP(C53,$H$2:$I$203,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" t="s">
-        <v>157</v>
-      </c>
-      <c r="D54">
-        <v>22</v>
-      </c>
-      <c r="E54" s="68">
-        <f>D54/(D54+D55+D56+D57)</f>
-        <v>0.14965986394557823</v>
-      </c>
-      <c r="F54" s="60" t="str">
-        <f>VLOOKUP(C54,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C55" t="s">
-        <v>38</v>
-      </c>
-      <c r="D55">
-        <v>75</v>
-      </c>
-      <c r="E55" s="68">
-        <f>D55/(D54+D55+D56+D57)</f>
-        <v>0.5102040816326531</v>
-      </c>
-      <c r="F55" s="60" t="str">
-        <f>VLOOKUP(C55,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" t="s">
-        <v>134</v>
-      </c>
-      <c r="D56">
-        <v>27</v>
-      </c>
-      <c r="E56" s="68">
-        <f>D56/(D54+D55+D56+D57)</f>
-        <v>0.1836734693877551</v>
-      </c>
-      <c r="F56" s="60" t="str">
-        <f>VLOOKUP(C56,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C57" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57">
-        <v>23</v>
-      </c>
-      <c r="E57" s="68">
-        <f>D57/(D54+D55+D56+D57)</f>
-        <v>0.1564625850340136</v>
-      </c>
-      <c r="F57" s="60" t="str">
-        <f>VLOOKUP(C57,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B58" s="75" t="s">
-        <v>50</v>
-      </c>
-      <c r="C58" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="68">
-        <v>1</v>
-      </c>
-      <c r="F58" s="60" t="str">
-        <f>VLOOKUP(C58,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B59" s="75" t="s">
-        <v>43</v>
-      </c>
-      <c r="C59" t="s">
-        <v>134</v>
-      </c>
-      <c r="E59" s="68">
-        <v>1</v>
-      </c>
-      <c r="F59" s="60" t="str">
-        <f>VLOOKUP(C59,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B60" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="C60" t="s">
-        <v>131</v>
-      </c>
-      <c r="E60" s="68">
-        <v>1</v>
-      </c>
-      <c r="F60" s="60" t="str">
-        <f>VLOOKUP(C60,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C61" t="s">
-        <v>136</v>
-      </c>
-      <c r="E61" s="68">
-        <v>1</v>
-      </c>
-      <c r="F61" s="60" t="str">
-        <f>VLOOKUP(C61,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" t="s">
-        <v>136</v>
-      </c>
-      <c r="E62" s="68">
-        <v>1</v>
-      </c>
-      <c r="F62" s="60" t="str">
-        <f>VLOOKUP(C62,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C63" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" s="68">
-        <v>1</v>
-      </c>
-      <c r="F63" s="60" t="str">
-        <f>VLOOKUP(C63,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C64" t="s">
-        <v>136</v>
-      </c>
-      <c r="E64" s="68">
-        <v>1</v>
-      </c>
-      <c r="F64" s="60" t="str">
-        <f>VLOOKUP(C64,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" s="68">
-        <v>1</v>
-      </c>
-      <c r="F65" s="60" t="str">
-        <f>VLOOKUP(C65,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" t="s">
-        <v>138</v>
-      </c>
-      <c r="E66" s="68">
-        <v>1</v>
-      </c>
-      <c r="F66" s="60" t="str">
-        <f>VLOOKUP(C66,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C67" t="s">
-        <v>138</v>
-      </c>
-      <c r="E67" s="68">
-        <v>1</v>
-      </c>
-      <c r="F67" s="60" t="str">
-        <f>VLOOKUP(C67,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B68" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" t="s">
-        <v>259</v>
-      </c>
-      <c r="E68" s="68">
-        <v>1</v>
-      </c>
-      <c r="F68" s="60" t="str">
-        <f>VLOOKUP(C68,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B69" s="80" t="s">
-        <v>39</v>
-      </c>
-      <c r="C69" t="s">
-        <v>259</v>
-      </c>
-      <c r="E69" s="68">
-        <v>1</v>
-      </c>
-      <c r="F69" s="60" t="str">
-        <f>VLOOKUP(C69,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="25">
-        <v>2022</v>
-      </c>
-      <c r="B70" s="80" t="s">
-        <v>37</v>
-      </c>
-      <c r="C70" t="s">
-        <v>259</v>
-      </c>
-      <c r="D70"/>
-      <c r="E70" s="68">
-        <v>1</v>
-      </c>
-      <c r="F70" s="60" t="str">
-        <f>VLOOKUP(C70,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="27">
-        <v>2022</v>
-      </c>
-      <c r="B71" s="81" t="s">
-        <v>100</v>
-      </c>
-      <c r="C71" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D71" s="28"/>
-      <c r="E71" s="67">
-        <v>1</v>
-      </c>
-      <c r="F71" s="60" t="str">
-        <f>VLOOKUP(C71,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="22">
-        <v>2024</v>
-      </c>
-      <c r="B72" s="109" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="D72" s="23"/>
-      <c r="E72" s="66">
-        <v>1</v>
-      </c>
-      <c r="F72" s="60" t="str">
-        <f>VLOOKUP(C72,$H$2:$I$203,2,0)</f>
-        <v>Gauche Révolutionnaire</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B73" s="90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C73" t="s">
-        <v>157</v>
-      </c>
-      <c r="E73" s="68">
-        <v>1</v>
-      </c>
-      <c r="F73" s="60" t="str">
-        <f>VLOOKUP(C73,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B74" s="90" t="s">
-        <v>32</v>
-      </c>
-      <c r="C74" t="s">
-        <v>38</v>
-      </c>
-      <c r="E74" s="68">
-        <v>1</v>
-      </c>
-      <c r="F74" s="60" t="str">
-        <f>VLOOKUP(C74,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B75" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" t="s">
-        <v>157</v>
-      </c>
-      <c r="D75">
-        <v>17</v>
-      </c>
-      <c r="E75" s="68">
-        <f>D75/(D75+D76+D77+D78)</f>
-        <v>8.808290155440414E-2</v>
-      </c>
-      <c r="F75" s="60" t="str">
-        <f>VLOOKUP(C75,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B76" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C76" t="s">
-        <v>38</v>
-      </c>
-      <c r="D76">
-        <v>72</v>
-      </c>
-      <c r="E76" s="68">
-        <f>D76/(D75+D76+D77+D78)</f>
-        <v>0.37305699481865284</v>
-      </c>
-      <c r="F76" s="60" t="str">
-        <f>VLOOKUP(C76,$H$2:$I$203,2,0)</f>
-        <v>Gauche Radical</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B77" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C77" t="s">
-        <v>134</v>
-      </c>
-      <c r="D77">
-        <v>66</v>
-      </c>
-      <c r="E77" s="68">
-        <f>D77/(D75+D76+D77+D78)</f>
-        <v>0.34196891191709844</v>
-      </c>
-      <c r="F77" s="60" t="str">
-        <f>VLOOKUP(C77,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B78" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="C78" t="s">
-        <v>131</v>
-      </c>
-      <c r="D78">
-        <v>38</v>
-      </c>
-      <c r="E78" s="68">
-        <f>D78/(D75+D76+D77+D78)</f>
-        <v>0.19689119170984457</v>
-      </c>
-      <c r="F78" s="60" t="str">
-        <f>VLOOKUP(C78,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B79" s="91" t="s">
-        <v>33</v>
-      </c>
-      <c r="C79" t="s">
-        <v>134</v>
-      </c>
-      <c r="E79" s="68">
-        <v>1</v>
-      </c>
-      <c r="F79" s="60" t="str">
-        <f>VLOOKUP(C79,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B80" s="91" t="s">
-        <v>50</v>
-      </c>
-      <c r="C80" t="s">
-        <v>134</v>
-      </c>
-      <c r="E80" s="68">
-        <v>1</v>
-      </c>
-      <c r="F80" s="60" t="str">
-        <f>VLOOKUP(C80,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B81" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="C81" t="s">
-        <v>134</v>
-      </c>
-      <c r="E81" s="68">
-        <v>1</v>
-      </c>
-      <c r="F81" s="60" t="str">
-        <f>VLOOKUP(C81,$H$2:$I$203,2,0)</f>
-        <v>Gauche Modéré</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B82" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="C82" t="s">
-        <v>131</v>
-      </c>
-      <c r="E82" s="68">
-        <v>1</v>
-      </c>
-      <c r="F82" s="60" t="str">
-        <f>VLOOKUP(C82,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B83" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="C83" t="s">
-        <v>131</v>
-      </c>
-      <c r="E83" s="68">
-        <v>1</v>
-      </c>
-      <c r="F83" s="60" t="str">
-        <f>VLOOKUP(C83,$H$2:$I$203,2,0)</f>
-        <v>Ecologiste</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B84" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="C84" t="s">
-        <v>136</v>
-      </c>
-      <c r="E84" s="68">
-        <v>1</v>
-      </c>
-      <c r="F84" s="60" t="str">
-        <f>VLOOKUP(C84,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B85" s="93" t="s">
-        <v>44</v>
-      </c>
-      <c r="C85" t="s">
-        <v>136</v>
-      </c>
-      <c r="E85" s="68">
-        <v>1</v>
-      </c>
-      <c r="F85" s="60" t="str">
-        <f>VLOOKUP(C85,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B86" s="93" t="s">
-        <v>45</v>
-      </c>
-      <c r="C86" t="s">
-        <v>136</v>
-      </c>
-      <c r="E86" s="68">
-        <v>1</v>
-      </c>
-      <c r="F86" s="60" t="str">
-        <f>VLOOKUP(C86,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B87" s="93" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" t="s">
-        <v>136</v>
-      </c>
-      <c r="E87" s="68">
-        <v>1</v>
-      </c>
-      <c r="F87" s="60" t="str">
-        <f>VLOOKUP(C87,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B88" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="C88" t="s">
-        <v>136</v>
-      </c>
-      <c r="E88" s="68">
-        <v>1</v>
-      </c>
-      <c r="F88" s="60" t="str">
-        <f>VLOOKUP(C88,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B89" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="C89" t="s">
-        <v>136</v>
-      </c>
-      <c r="E89" s="68">
-        <v>1</v>
-      </c>
-      <c r="F89" s="60" t="str">
-        <f>VLOOKUP(C89,$H$2:$I$203,2,0)</f>
-        <v>Centre</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B90" s="94" t="s">
-        <v>31</v>
-      </c>
-      <c r="C90" t="s">
-        <v>138</v>
-      </c>
-      <c r="E90" s="68">
-        <v>1</v>
-      </c>
-      <c r="F90" s="60" t="str">
-        <f>VLOOKUP(C90,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B91" s="94" t="s">
-        <v>26</v>
-      </c>
-      <c r="C91" t="s">
-        <v>138</v>
-      </c>
-      <c r="E91" s="68">
-        <v>1</v>
-      </c>
-      <c r="F91" s="60" t="str">
-        <f>VLOOKUP(C91,$H$2:$I$203,2,0)</f>
-        <v>Droite</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B92" s="95" t="s">
-        <v>37</v>
-      </c>
-      <c r="C92" t="s">
-        <v>259</v>
-      </c>
-      <c r="E92" s="68">
-        <v>1</v>
-      </c>
-      <c r="F92" s="60" t="str">
-        <f>VLOOKUP(C92,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B93" s="95" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" t="s">
-        <v>259</v>
-      </c>
-      <c r="E93" s="68">
-        <v>1</v>
-      </c>
-      <c r="F93" s="60" t="str">
-        <f>VLOOKUP(C93,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B94" s="95" t="s">
-        <v>39</v>
-      </c>
-      <c r="C94" t="s">
-        <v>259</v>
-      </c>
-      <c r="E94" s="68">
-        <v>1</v>
-      </c>
-      <c r="F94" s="60" t="str">
-        <f>VLOOKUP(C94,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="25">
-        <v>2024</v>
-      </c>
-      <c r="B95" s="95" t="s">
-        <v>48</v>
-      </c>
-      <c r="C95" t="s">
-        <v>259</v>
-      </c>
-      <c r="E95" s="68">
-        <v>1</v>
-      </c>
-      <c r="F95" s="60" t="str">
-        <f>VLOOKUP(C95,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="27">
-        <v>2024</v>
-      </c>
-      <c r="B96" s="96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C96" s="28" t="s">
-        <v>259</v>
-      </c>
-      <c r="D96" s="28"/>
-      <c r="E96" s="67">
-        <v>1</v>
-      </c>
-      <c r="F96" s="60" t="str">
-        <f>VLOOKUP(C96,$H$2:$I$203,2,0)</f>
-        <v>Extrème Droite</v>
+      <c r="G53" s="125" t="s">
+        <v>330</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A39:G39"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data_Election.xlsx
+++ b/Data_Election.xlsx
@@ -9,14 +9,1088 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682"/>
+    <workbookView xWindow="480" yWindow="75" windowWidth="18195" windowHeight="11820" tabRatio="682" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Nuances" sheetId="10" r:id="rId3"/>
+    <sheet name="CompositionAN" sheetId="11" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="B4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+FG
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe 
+GDR
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe ECOLO
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SRC
+279+16=295</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe RRDP
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe UDI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe UDI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe UMP
+185+11=196
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NG
+28+3=31
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe GDR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe MODEM
+43+4=47</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LC:
+34+1=35
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LR
+95+5=100
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E28" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LREM
+309+5=314</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E11" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LREM
+309+5=314
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI-NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe GDR-NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe Ecologiste-NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SOC
+27+4=31
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe REN
+168+4=172
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe DEM
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe HOR
+28+2=30
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LR
+59+3=62
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LIOT
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI
+71+1=72
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe GDR
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe ECOS
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SOC
+62+4=66
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe EPR
+84+12=96
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LIOT
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe HOR
+25+8=33
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I27" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe DR
+41+6=47
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe UDR
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I31" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe RN
+123+3=126
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LD
+35+1=36
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Union Gauche
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1217,6 +2291,36 @@
   </si>
   <si>
     <t>NFP 2024 — idem</t>
+  </si>
+  <si>
+    <t>Nuance Officielle</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>2012 Ministere</t>
+  </si>
+  <si>
+    <t>2012 Groupe</t>
+  </si>
+  <si>
+    <t>2017 Ministere</t>
+  </si>
+  <si>
+    <t>2017 Groupe</t>
+  </si>
+  <si>
+    <t>2022 Ministere</t>
+  </si>
+  <si>
+    <t>2022 Groupe</t>
+  </si>
+  <si>
+    <t>2024 Ministere</t>
+  </si>
+  <si>
+    <t>2024 Groupe</t>
   </si>
 </sst>
 </file>
@@ -13423,6 +14527,643 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" width="13.26953125" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" width="13.26953125" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" width="11.6328125" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" width="13.26953125" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" width="11.6328125" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" width="11.6328125" customWidth="1" bestFit="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C1" t="s">
+        <v>334</v>
+      </c>
+      <c r="D1" t="s">
+        <v>335</v>
+      </c>
+      <c r="E1" t="s">
+        <v>336</v>
+      </c>
+      <c r="F1" t="s">
+        <v>337</v>
+      </c>
+      <c r="G1" t="s">
+        <v>338</v>
+      </c>
+      <c r="H1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="121" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="121" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="7">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
+      </c>
+      <c r="F4" s="7">
+        <v>131</v>
+      </c>
+      <c r="G4">
+        <v>22</v>
+      </c>
+      <c r="H4" s="7">
+        <v>178</v>
+      </c>
+      <c r="I4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5">
+        <v>17</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7"/>
+      <c r="G5">
+        <v>75</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="128" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6">
+        <v>280</v>
+      </c>
+      <c r="C6" s="7">
+        <v>295</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6" s="7">
+        <v>31</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6">
+        <v>31</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>22</v>
+      </c>
+      <c r="C8">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>22</v>
+      </c>
+      <c r="H8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>18</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="130" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="7">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7">
+        <v>314</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="H11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="130" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17">
+        <v>12</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18">
+        <v>308</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="H18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="F19">
+        <v>245</v>
+      </c>
+      <c r="G19">
+        <v>172</v>
+      </c>
+      <c r="H19">
+        <v>150</v>
+      </c>
+      <c r="I19">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20">
+        <v>42</v>
+      </c>
+      <c r="E20">
+        <v>47</v>
+      </c>
+      <c r="G20">
+        <v>48</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="130" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21">
+        <v>18</v>
+      </c>
+      <c r="E21">
+        <v>35</v>
+      </c>
+      <c r="F21">
+        <v>3</v>
+      </c>
+      <c r="G21">
+        <v>16</v>
+      </c>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="130" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="130" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23">
+        <v>4</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="130" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="130" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26">
+        <v>194</v>
+      </c>
+      <c r="C26" s="7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="131" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27">
+        <v>112</v>
+      </c>
+      <c r="E27">
+        <v>100</v>
+      </c>
+      <c r="F27">
+        <v>61</v>
+      </c>
+      <c r="G27">
+        <v>62</v>
+      </c>
+      <c r="H27">
+        <v>39</v>
+      </c>
+      <c r="I27">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="131" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28">
+        <v>15</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28">
+        <v>6</v>
+      </c>
+      <c r="E28" s="7">
+        <v>17</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="H28">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7">
+        <v>8</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31">
+        <v>89</v>
+      </c>
+      <c r="G31">
+        <v>89</v>
+      </c>
+      <c r="H31">
+        <v>125</v>
+      </c>
+      <c r="I31">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32" s="7"/>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="G32">
+        <v>9</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="132" t="s">
+        <v>100</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="132" t="s">
+        <v>39</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="132" t="s">
+        <v>48</v>
+      </c>
+      <c r="F35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="132" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36">
+        <v>17</v>
+      </c>
+      <c r="I36">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="132" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38">
+        <f>SUM(B2:B37)</f>
+        <v>577</v>
+      </c>
+      <c r="C38">
+        <f>SUM(C2:C37)</f>
+        <v>577</v>
+      </c>
+      <c r="D38">
+        <f>SUM(D2:D37)</f>
+        <v>577</v>
+      </c>
+      <c r="E38">
+        <f>SUM(E2:E37)</f>
+        <v>577</v>
+      </c>
+      <c r="F38">
+        <f>SUM(F2:F37)</f>
+        <v>577</v>
+      </c>
+      <c r="G38">
+        <f>SUM(G2:G37)</f>
+        <v>577</v>
+      </c>
+      <c r="H38">
+        <f>SUM(H2:H37)</f>
+        <v>577</v>
+      </c>
+      <c r="I38">
+        <f>SUM(I2:I37)</f>
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="C11:C21"/>
+    <mergeCell ref="E11:E18"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="E28:E32"/>
+    <mergeCell ref="C30:C32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" defaultColWidth="8.6796875"/>

--- a/Data_Election.xlsx
+++ b/Data_Election.xlsx
@@ -14,13 +14,13 @@
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="Nuances" sheetId="10" r:id="rId3"/>
-    <sheet name="CompositionAN" sheetId="11" r:id="rId2"/>
+    <sheet name="Règle" sheetId="12" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
@@ -46,7 +46,8 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-FG
+Groupe 
+GDR
 </t>
         </r>
       </text>
@@ -71,13 +72,315 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Groupe 
-GDR
+Groupe GDR</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe GDR-NUPES
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="C10" authorId="0">
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe GDR
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI-NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E5" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LFI
+71+1=72
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SRC
+279+16=295</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NG
+28+3=31
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SOC
+27+4=31
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E6" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe SOC
+62+4=66
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe RRDP
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe Ecologiste-NUPES
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe ECOS
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
@@ -102,57 +405,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe SRC
-279+16=295</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe RRDP
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C21" authorId="0">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -196,11 +449,318 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
+Groupe LREM
+309+5=314
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LREM
+309+5=314</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe REN
+168+4=172
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe EPR
+84+12=96
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe MODEM
+43+4=47</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe DEM
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E20" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LD
+35+1=36
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
 Groupe UDI</t>
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0">
+    <comment ref="C21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LC:
+34+1=35
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LIOT
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E21" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe LIOT
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe HOR
+28+2=30
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E22" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe HOR
+25+8=33
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -226,158 +786,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C30" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe NI
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe NG
-28+3=31
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe GDR</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LFI
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe MODEM
-43+4=47</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LC:
-34+1=35
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E27" authorId="0">
+    <comment ref="C27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -403,285 +812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E28" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe NI</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E18" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LREM
-309+5=314</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LREM
-309+5=314
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-NUPES
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LFI-NUPES
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe GDR-NUPES
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe Ecologiste-NUPES
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe SOC
-27+4=31
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe REN
-168+4=172
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe DEM
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe HOR
-28+2=30
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G27" authorId="0">
+    <comment ref="D27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -707,236 +838,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LIOT
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G32" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe NI
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LFI
-71+1=72
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe GDR
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe ECOS
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I6" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe SOC
-62+4=66
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I19" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe EPR
-84+12=96
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I21" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LIOT
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I22" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe HOR
-25+8=33
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I27" authorId="0">
+    <comment ref="E27" authorId="0">
       <text>
         <r>
           <rPr>
@@ -962,7 +864,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I36" authorId="0">
+    <comment ref="C28" authorId="0">
       <text>
         <r>
           <rPr>
@@ -982,12 +884,36 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Groupe UDR
+Groupe NI</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B30" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe NI
 </t>
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0">
+    <comment ref="E31" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1013,33 +939,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">Pepinou Token:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Groupe LD
-35+1=36
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I32" authorId="0">
+    <comment ref="D32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1064,7 +964,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H4" authorId="0">
+    <comment ref="E32" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1084,7 +984,32 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-Union Gauche
+Groupe NI
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E36" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">Pepinou Token:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Groupe UDR
 </t>
         </r>
       </text>
@@ -14527,643 +14452,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" width="13.26953125" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" width="11.6328125" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" width="13.26953125" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" width="11.6328125" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" width="13.26953125" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" width="11.6328125" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" width="11.6328125" customWidth="1" bestFit="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B1" t="s">
-        <v>333</v>
-      </c>
-      <c r="C1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D1" t="s">
-        <v>335</v>
-      </c>
-      <c r="E1" t="s">
-        <v>336</v>
-      </c>
-      <c r="F1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H1" t="s">
-        <v>339</v>
-      </c>
-      <c r="I1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="121" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="121" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="126" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="7">
-        <v>10</v>
-      </c>
-      <c r="C4" s="7">
-        <v>15</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-      <c r="E4">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7">
-        <v>131</v>
-      </c>
-      <c r="G4">
-        <v>22</v>
-      </c>
-      <c r="H4" s="7">
-        <v>178</v>
-      </c>
-      <c r="I4">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="127" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>17</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5">
-        <v>75</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="128" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6">
-        <v>280</v>
-      </c>
-      <c r="C6" s="7">
-        <v>295</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6" s="7">
-        <v>31</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6">
-        <v>31</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="128" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7">
-        <v>12</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="7"/>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="128" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8">
-        <v>22</v>
-      </c>
-      <c r="C8">
-        <v>16</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="F8">
-        <v>22</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="129" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>23</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="129" t="s">
-        <v>51</v>
-      </c>
-      <c r="B10">
-        <v>17</v>
-      </c>
-      <c r="C10">
-        <v>18</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="130" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11">
-        <v>2</v>
-      </c>
-      <c r="C11" s="7">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>314</v>
-      </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="H11">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="130" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="130" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="E13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="130" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="130" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15">
-        <v>2</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="E15" s="7"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="130" t="s">
-        <v>85</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="E16" s="7"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="130" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17">
-        <v>12</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="E17" s="7"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="130" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18">
-        <v>308</v>
-      </c>
-      <c r="E18" s="7"/>
-      <c r="H18"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="130" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="F19">
-        <v>245</v>
-      </c>
-      <c r="G19">
-        <v>172</v>
-      </c>
-      <c r="H19">
-        <v>150</v>
-      </c>
-      <c r="I19">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="130" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>47</v>
-      </c>
-      <c r="G20">
-        <v>48</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="130" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21">
-        <v>18</v>
-      </c>
-      <c r="E21">
-        <v>35</v>
-      </c>
-      <c r="F21">
-        <v>3</v>
-      </c>
-      <c r="G21">
-        <v>16</v>
-      </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="130" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22">
-        <v>30</v>
-      </c>
-      <c r="H22">
-        <v>6</v>
-      </c>
-      <c r="I22">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="130" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23">
-        <v>4</v>
-      </c>
-      <c r="H23">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="130" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="130" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="131" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26">
-        <v>194</v>
-      </c>
-      <c r="C26" s="7">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="131" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27">
-        <v>112</v>
-      </c>
-      <c r="E27">
-        <v>100</v>
-      </c>
-      <c r="F27">
-        <v>61</v>
-      </c>
-      <c r="G27">
-        <v>62</v>
-      </c>
-      <c r="H27">
-        <v>39</v>
-      </c>
-      <c r="I27">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="131" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28">
-        <v>15</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28">
-        <v>6</v>
-      </c>
-      <c r="E28" s="7">
-        <v>17</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-      <c r="H28">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="132" t="s">
-        <v>34</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" s="7"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="132" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30">
-        <v>2</v>
-      </c>
-      <c r="C30" s="7">
-        <v>8</v>
-      </c>
-      <c r="D30">
-        <v>8</v>
-      </c>
-      <c r="E30" s="7"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="132" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31">
-        <v>89</v>
-      </c>
-      <c r="G31">
-        <v>89</v>
-      </c>
-      <c r="H31">
-        <v>125</v>
-      </c>
-      <c r="I31">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="132" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-      <c r="C32" s="7"/>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" s="7"/>
-      <c r="G32">
-        <v>9</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-      <c r="I32">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="132" t="s">
-        <v>100</v>
-      </c>
-      <c r="F33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="132" t="s">
-        <v>39</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="132" t="s">
-        <v>48</v>
-      </c>
-      <c r="F35">
-        <v>1</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="132" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36">
-        <v>17</v>
-      </c>
-      <c r="I36">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="132" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38">
-        <f>SUM(B2:B37)</f>
-        <v>577</v>
-      </c>
-      <c r="C38">
-        <f>SUM(C2:C37)</f>
-        <v>577</v>
-      </c>
-      <c r="D38">
-        <f>SUM(D2:D37)</f>
-        <v>577</v>
-      </c>
-      <c r="E38">
-        <f>SUM(E2:E37)</f>
-        <v>577</v>
-      </c>
-      <c r="F38">
-        <f>SUM(F2:F37)</f>
-        <v>577</v>
-      </c>
-      <c r="G38">
-        <f>SUM(G2:G37)</f>
-        <v>577</v>
-      </c>
-      <c r="H38">
-        <f>SUM(H2:H37)</f>
-        <v>577</v>
-      </c>
-      <c r="I38">
-        <f>SUM(I2:I37)</f>
-        <v>577</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="C11:C21"/>
-    <mergeCell ref="E11:E18"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="E28:E32"/>
-    <mergeCell ref="C30:C32"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" defaultColWidth="8.6796875"/>
@@ -16322,4 +15610,388 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" defaultColWidth="8.7265625"/>
+  <cols>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" customWidth="1"/>
+    <col min="3" max="3" width="11.6328125" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>331</v>
+      </c>
+      <c r="B1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" t="s">
+        <v>338</v>
+      </c>
+      <c r="E1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="121" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="121" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="7">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
+      <c r="E4">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="127" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="7"/>
+      <c r="C5">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>75</v>
+      </c>
+      <c r="E5">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="128" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7">
+        <v>295</v>
+      </c>
+      <c r="C6" s="7">
+        <v>31</v>
+      </c>
+      <c r="D6">
+        <v>31</v>
+      </c>
+      <c r="E6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="128" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="128" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="129" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="130" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="7">
+        <v>29</v>
+      </c>
+      <c r="C11" s="7">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="130" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="130" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="130" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="130" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="130" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="130" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="130" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="D19">
+        <v>172</v>
+      </c>
+      <c r="E19">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="130" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20">
+        <v>47</v>
+      </c>
+      <c r="D20">
+        <v>48</v>
+      </c>
+      <c r="E20">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="130" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21">
+        <v>35</v>
+      </c>
+      <c r="D21">
+        <v>16</v>
+      </c>
+      <c r="E21">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="130" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="130" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="130" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="130" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="131" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27">
+        <v>100</v>
+      </c>
+      <c r="D27">
+        <v>62</v>
+      </c>
+      <c r="E27">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="131" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="132" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="7">
+        <v>8</v>
+      </c>
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="132" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31">
+        <v>89</v>
+      </c>
+      <c r="E31">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="132" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32">
+        <v>9</v>
+      </c>
+      <c r="E32">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="132" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="132" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="132" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="132" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="132" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38">
+        <f>SUM(B2:B37)</f>
+        <v>577</v>
+      </c>
+      <c r="C38">
+        <f>SUM(C2:C37)</f>
+        <v>577</v>
+      </c>
+      <c r="D38">
+        <f>SUM(D2:D37)</f>
+        <v>577</v>
+      </c>
+      <c r="E38">
+        <f>SUM(E2:E37)</f>
+        <v>577</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B11:B21"/>
+    <mergeCell ref="C11:C18"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="C28:C32"/>
+    <mergeCell ref="B30:B32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
 </file>